--- a/research/traditional_assets/database/data/croatia/croatia_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_telecom_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0773956929436591</v>
+        <v>0.07729328069636052</v>
       </c>
       <c r="C2">
-        <v>3301.287231031357</v>
+        <v>3274.621135931076</v>
       </c>
       <c r="D2">
-        <v>3067.487231031357</v>
+        <v>3073.822135931076</v>
       </c>
       <c r="E2">
-        <v>-87.59999999999999</v>
+        <v>-54.599</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>33.001</v>
       </c>
       <c r="G2">
         <v>233.8</v>
@@ -1451,28 +1451,28 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.6599503</v>
       </c>
       <c r="N2">
-        <v>92.09999999999997</v>
+        <v>90.44004969999996</v>
       </c>
       <c r="O2">
-        <v>16.57799999999999</v>
+        <v>16.27920894599999</v>
       </c>
       <c r="P2">
-        <v>75.52199999999998</v>
+        <v>74.16084075399996</v>
       </c>
       <c r="Q2">
-        <v>377.122</v>
+        <v>375.760840754</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0773956929436591</v>
+        <v>0.0776573946427884</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.5371614406989589</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>55.48358887612477</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07729328069636052</v>
+        <v>0.07719086844906194</v>
       </c>
       <c r="C3">
-        <v>3274.621135931076</v>
+        <v>3247.981260382006</v>
       </c>
       <c r="D3">
-        <v>3073.822135931076</v>
+        <v>3080.183260382006</v>
       </c>
       <c r="E3">
-        <v>-54.599</v>
+        <v>-21.598</v>
       </c>
       <c r="F3">
-        <v>33.001</v>
+        <v>66.002</v>
       </c>
       <c r="G3">
         <v>233.8</v>
@@ -1533,28 +1533,28 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M3">
-        <v>1.6599503</v>
+        <v>3.3199006</v>
       </c>
       <c r="N3">
-        <v>90.44004969999996</v>
+        <v>88.78009939999997</v>
       </c>
       <c r="O3">
-        <v>16.27920894599999</v>
+        <v>15.98041789199999</v>
       </c>
       <c r="P3">
-        <v>74.16084075399996</v>
+        <v>72.79968150799998</v>
       </c>
       <c r="Q3">
-        <v>375.760840754</v>
+        <v>374.399681508</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0776573946427884</v>
+        <v>0.07792443719292033</v>
       </c>
       <c r="T3">
-        <v>0.5371614406989589</v>
+        <v>0.5416641617332814</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>55.48358887612477</v>
+        <v>27.74179443806239</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07719086844906194</v>
+        <v>0.07708845620176333</v>
       </c>
       <c r="C4">
-        <v>3247.981260382006</v>
+        <v>3221.367767501946</v>
       </c>
       <c r="D4">
-        <v>3080.183260382006</v>
+        <v>3086.570767501946</v>
       </c>
       <c r="E4">
-        <v>-21.598</v>
+        <v>11.40300000000001</v>
       </c>
       <c r="F4">
-        <v>66.002</v>
+        <v>99.003</v>
       </c>
       <c r="G4">
         <v>233.8</v>
@@ -1615,28 +1615,28 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M4">
-        <v>3.3199006</v>
+        <v>4.9798509</v>
       </c>
       <c r="N4">
-        <v>88.78009939999997</v>
+        <v>87.12014909999996</v>
       </c>
       <c r="O4">
-        <v>15.98041789199999</v>
+        <v>15.68162683799999</v>
       </c>
       <c r="P4">
-        <v>72.79968150799998</v>
+        <v>71.43852226199996</v>
       </c>
       <c r="Q4">
-        <v>374.399681508</v>
+        <v>373.038522262</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07792443719292033</v>
+        <v>0.07819698577501374</v>
       </c>
       <c r="T4">
-        <v>0.5416641617332814</v>
+        <v>0.546259722376559</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>27.74179443806239</v>
+        <v>18.49452962537492</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07708845620176333</v>
+        <v>0.07698604395446475</v>
       </c>
       <c r="C5">
-        <v>3221.367767501946</v>
+        <v>3194.780821764558</v>
       </c>
       <c r="D5">
-        <v>3086.570767501946</v>
+        <v>3092.984821764558</v>
       </c>
       <c r="E5">
-        <v>11.40300000000001</v>
+        <v>44.404</v>
       </c>
       <c r="F5">
-        <v>99.003</v>
+        <v>132.004</v>
       </c>
       <c r="G5">
         <v>233.8</v>
@@ -1697,28 +1697,28 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M5">
-        <v>4.9798509</v>
+        <v>6.639801199999999</v>
       </c>
       <c r="N5">
-        <v>87.12014909999996</v>
+        <v>85.46019879999997</v>
       </c>
       <c r="O5">
-        <v>15.68162683799999</v>
+        <v>15.38283578399999</v>
       </c>
       <c r="P5">
-        <v>71.43852226199996</v>
+        <v>70.07736301599998</v>
       </c>
       <c r="Q5">
-        <v>373.038522262</v>
+        <v>371.677363016</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07819698577501374</v>
+        <v>0.07847521245256744</v>
       </c>
       <c r="T5">
-        <v>0.546259722376559</v>
+        <v>0.5509510238665715</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>18.49452962537492</v>
+        <v>13.87089721903119</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07698604395446475</v>
+        <v>0.07694513170716616</v>
       </c>
       <c r="C6">
-        <v>3194.780821764558</v>
+        <v>3164.349603864698</v>
       </c>
       <c r="D6">
-        <v>3092.984821764558</v>
+        <v>3095.554603864698</v>
       </c>
       <c r="E6">
-        <v>44.404</v>
+        <v>77.405</v>
       </c>
       <c r="F6">
-        <v>132.004</v>
+        <v>165.005</v>
       </c>
       <c r="G6">
         <v>233.8</v>
@@ -1779,45 +1779,45 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M6">
-        <v>6.639801199999999</v>
+        <v>8.547259</v>
       </c>
       <c r="N6">
-        <v>85.46019879999997</v>
+        <v>83.55274099999997</v>
       </c>
       <c r="O6">
-        <v>15.38283578399999</v>
+        <v>15.03949337999999</v>
       </c>
       <c r="P6">
-        <v>70.07736301599998</v>
+        <v>68.51324761999997</v>
       </c>
       <c r="Q6">
-        <v>371.677363016</v>
+        <v>370.11324762</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07847521245256744</v>
+        <v>0.07875929653385913</v>
       </c>
       <c r="T6">
-        <v>0.5509510238665715</v>
+        <v>0.555741089598479</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.18</v>
       </c>
       <c r="W6">
-        <v>0.041246</v>
+        <v>0.042476</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>13.87089721903119</v>
+        <v>10.77538424891535</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07694513170716616</v>
+        <v>0.07693865945986758</v>
       </c>
       <c r="C7">
-        <v>3164.349603864698</v>
+        <v>3131.755530234032</v>
       </c>
       <c r="D7">
-        <v>3095.554603864698</v>
+        <v>3095.961530234032</v>
       </c>
       <c r="E7">
-        <v>77.405</v>
+        <v>110.406</v>
       </c>
       <c r="F7">
-        <v>165.005</v>
+        <v>198.006</v>
       </c>
       <c r="G7">
         <v>233.8</v>
@@ -1861,45 +1861,45 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M7">
-        <v>8.547259</v>
+        <v>10.593321</v>
       </c>
       <c r="N7">
-        <v>83.55274099999997</v>
+        <v>81.50667899999996</v>
       </c>
       <c r="O7">
-        <v>15.03949337999999</v>
+        <v>14.67120221999999</v>
       </c>
       <c r="P7">
-        <v>68.51324761999997</v>
+        <v>66.83547677999996</v>
       </c>
       <c r="Q7">
-        <v>370.11324762</v>
+        <v>368.43547678</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07875929653385913</v>
+        <v>0.07904942495730594</v>
       </c>
       <c r="T7">
-        <v>0.555741089598479</v>
+        <v>0.5606330716225547</v>
       </c>
       <c r="U7">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V7">
         <v>0.18</v>
       </c>
       <c r="W7">
-        <v>0.042476</v>
+        <v>0.04387</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>10.77538424891535</v>
+        <v>8.694157384638865</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07693865945986758</v>
+        <v>0.076908407212569</v>
       </c>
       <c r="C8">
-        <v>3131.755530234032</v>
+        <v>3100.657984248748</v>
       </c>
       <c r="D8">
-        <v>3095.961530234032</v>
+        <v>3097.864984248748</v>
       </c>
       <c r="E8">
-        <v>110.406</v>
+        <v>143.407</v>
       </c>
       <c r="F8">
-        <v>198.006</v>
+        <v>231.007</v>
       </c>
       <c r="G8">
         <v>233.8</v>
@@ -1943,45 +1943,45 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M8">
-        <v>10.593321</v>
+        <v>12.5436801</v>
       </c>
       <c r="N8">
-        <v>81.50667899999996</v>
+        <v>79.55631989999996</v>
       </c>
       <c r="O8">
-        <v>14.67120221999999</v>
+        <v>14.32013758199999</v>
       </c>
       <c r="P8">
-        <v>66.83547677999996</v>
+        <v>65.23618231799998</v>
       </c>
       <c r="Q8">
-        <v>368.43547678</v>
+        <v>366.836182318</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07904942495730594</v>
+        <v>0.0793457927016871</v>
       </c>
       <c r="T8">
-        <v>0.5606330716225547</v>
+        <v>0.5656302575611267</v>
       </c>
       <c r="U8">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V8">
         <v>0.18</v>
       </c>
       <c r="W8">
-        <v>0.04387</v>
+        <v>0.044526</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y8">
-        <v>8.694157384638865</v>
+        <v>7.342342858376942</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.076908407212569</v>
+        <v>0.07683879496527041</v>
       </c>
       <c r="C9">
-        <v>3100.657984248748</v>
+        <v>3072.045848802272</v>
       </c>
       <c r="D9">
-        <v>3097.864984248748</v>
+        <v>3102.253848802271</v>
       </c>
       <c r="E9">
-        <v>143.407</v>
+        <v>176.408</v>
       </c>
       <c r="F9">
-        <v>231.007</v>
+        <v>264.008</v>
       </c>
       <c r="G9">
         <v>233.8</v>
@@ -2025,28 +2025,28 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M9">
-        <v>12.5436801</v>
+        <v>14.3356344</v>
       </c>
       <c r="N9">
-        <v>79.55631989999996</v>
+        <v>77.76436559999996</v>
       </c>
       <c r="O9">
-        <v>14.32013758199999</v>
+        <v>13.99758580799999</v>
       </c>
       <c r="P9">
-        <v>65.23618231799998</v>
+        <v>63.76677979199997</v>
       </c>
       <c r="Q9">
-        <v>366.836182318</v>
+        <v>365.366779792</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0793457927016871</v>
+        <v>0.07964860322312001</v>
       </c>
       <c r="T9">
-        <v>0.5656302575611267</v>
+        <v>0.5707360779766243</v>
       </c>
       <c r="U9">
         <v>0.0543</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>7.342342858376941</v>
+        <v>6.424550001079824</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07683879496527041</v>
+        <v>0.07684298271797183</v>
       </c>
       <c r="C10">
-        <v>3072.045848802272</v>
+        <v>3038.780470758488</v>
       </c>
       <c r="D10">
-        <v>3102.253848802271</v>
+        <v>3101.989470758488</v>
       </c>
       <c r="E10">
-        <v>176.408</v>
+        <v>209.409</v>
       </c>
       <c r="F10">
-        <v>264.008</v>
+        <v>297.009</v>
       </c>
       <c r="G10">
         <v>233.8</v>
@@ -2107,45 +2107,45 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M10">
-        <v>14.3356344</v>
+        <v>16.4245977</v>
       </c>
       <c r="N10">
-        <v>77.76436559999996</v>
+        <v>75.67540229999997</v>
       </c>
       <c r="O10">
-        <v>13.99758580799999</v>
+        <v>13.62157241399999</v>
       </c>
       <c r="P10">
-        <v>63.76677979199997</v>
+        <v>62.05382988599998</v>
       </c>
       <c r="Q10">
-        <v>365.366779792</v>
+        <v>363.653829886</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07964860322312001</v>
+        <v>0.07995806892084815</v>
       </c>
       <c r="T10">
-        <v>0.5707360779766243</v>
+        <v>0.5759541142254294</v>
       </c>
       <c r="U10">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V10">
         <v>0.18</v>
       </c>
       <c r="W10">
-        <v>0.044526</v>
+        <v>0.045346</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y10">
-        <v>6.424550001079824</v>
+        <v>5.607443280026272</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07684298271797183</v>
+        <v>0.07678157047067323</v>
       </c>
       <c r="C11">
-        <v>3038.780470758488</v>
+        <v>3009.661022969547</v>
       </c>
       <c r="D11">
-        <v>3101.989470758488</v>
+        <v>3105.871022969547</v>
       </c>
       <c r="E11">
-        <v>209.409</v>
+        <v>242.41</v>
       </c>
       <c r="F11">
-        <v>297.009</v>
+        <v>330.01</v>
       </c>
       <c r="G11">
         <v>233.8</v>
@@ -2189,28 +2189,28 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M11">
-        <v>16.4245977</v>
+        <v>18.249553</v>
       </c>
       <c r="N11">
-        <v>75.67540229999997</v>
+        <v>73.85044699999997</v>
       </c>
       <c r="O11">
-        <v>13.62157241399999</v>
+        <v>13.29308046</v>
       </c>
       <c r="P11">
-        <v>62.05382988599998</v>
+        <v>60.55736653999998</v>
       </c>
       <c r="Q11">
-        <v>363.653829886</v>
+        <v>362.15736654</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07995806892084815</v>
+        <v>0.08027441163408136</v>
       </c>
       <c r="T11">
-        <v>0.5759541142254294</v>
+        <v>0.5812881068353191</v>
       </c>
       <c r="U11">
         <v>0.0553</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>5.607443280026272</v>
+        <v>5.046698952023646</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07678157047067323</v>
+        <v>0.07672015822337465</v>
       </c>
       <c r="C12">
-        <v>3009.661022969547</v>
+        <v>2980.551301405749</v>
       </c>
       <c r="D12">
-        <v>3105.871022969547</v>
+        <v>3109.762301405749</v>
       </c>
       <c r="E12">
-        <v>242.41</v>
+        <v>275.4109999999999</v>
       </c>
       <c r="F12">
-        <v>330.01</v>
+        <v>363.011</v>
       </c>
       <c r="G12">
         <v>233.8</v>
@@ -2271,28 +2271,28 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M12">
-        <v>18.249553</v>
+        <v>20.0745083</v>
       </c>
       <c r="N12">
-        <v>73.85044699999997</v>
+        <v>72.02549169999998</v>
       </c>
       <c r="O12">
-        <v>13.29308046</v>
+        <v>12.96458850599999</v>
       </c>
       <c r="P12">
-        <v>60.55736653999998</v>
+        <v>59.06090319399998</v>
       </c>
       <c r="Q12">
-        <v>362.15736654</v>
+        <v>360.660903194</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08027441163408136</v>
+        <v>0.08059786317233106</v>
       </c>
       <c r="T12">
-        <v>0.5812881068353191</v>
+        <v>0.5867419644476781</v>
       </c>
       <c r="U12">
         <v>0.0553</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>5.046698952023646</v>
+        <v>4.587908138203314</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07672015822337465</v>
+        <v>0.07690474597607606</v>
       </c>
       <c r="C13">
-        <v>2980.551301405749</v>
+        <v>2935.883505928741</v>
       </c>
       <c r="D13">
-        <v>3109.762301405749</v>
+        <v>3098.095505928741</v>
       </c>
       <c r="E13">
-        <v>275.4109999999999</v>
+        <v>308.412</v>
       </c>
       <c r="F13">
-        <v>363.011</v>
+        <v>396.012</v>
       </c>
       <c r="G13">
         <v>233.8</v>
@@ -2353,45 +2353,45 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M13">
-        <v>20.0745083</v>
+        <v>22.8894936</v>
       </c>
       <c r="N13">
-        <v>72.02549169999998</v>
+        <v>69.21050639999996</v>
       </c>
       <c r="O13">
-        <v>12.96458850599999</v>
+        <v>12.45789115199999</v>
       </c>
       <c r="P13">
-        <v>59.06090319399998</v>
+        <v>56.75261524799997</v>
       </c>
       <c r="Q13">
-        <v>360.660903194</v>
+        <v>358.352615248</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08059786317233106</v>
+        <v>0.08092866588190462</v>
       </c>
       <c r="T13">
-        <v>0.5867419644476781</v>
+        <v>0.5923197733694091</v>
       </c>
       <c r="U13">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V13">
         <v>0.18</v>
       </c>
       <c r="W13">
-        <v>0.045346</v>
+        <v>0.04739600000000001</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y13">
-        <v>4.587908138203314</v>
+        <v>4.023680104482519</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07690474597607606</v>
+        <v>0.07723693372877748</v>
       </c>
       <c r="C14">
-        <v>2935.883505928741</v>
+        <v>2882.105756212505</v>
       </c>
       <c r="D14">
-        <v>3098.095505928741</v>
+        <v>3077.318756212505</v>
       </c>
       <c r="E14">
-        <v>308.412</v>
+        <v>341.413</v>
       </c>
       <c r="F14">
-        <v>396.012</v>
+        <v>429.013</v>
       </c>
       <c r="G14">
         <v>233.8</v>
@@ -2435,45 +2435,45 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M14">
-        <v>22.8894936</v>
+        <v>26.2984969</v>
       </c>
       <c r="N14">
-        <v>69.21050639999996</v>
+        <v>65.80150309999996</v>
       </c>
       <c r="O14">
-        <v>12.45789115199999</v>
+        <v>11.84427055799999</v>
       </c>
       <c r="P14">
-        <v>56.75261524799997</v>
+        <v>53.95723254199997</v>
       </c>
       <c r="Q14">
-        <v>358.352615248</v>
+        <v>355.557232542</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08092866588190462</v>
+        <v>0.08126707325146837</v>
       </c>
       <c r="T14">
-        <v>0.5923197733694091</v>
+        <v>0.5980258077835936</v>
       </c>
       <c r="U14">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V14">
         <v>0.18</v>
       </c>
       <c r="W14">
-        <v>0.04739600000000001</v>
+        <v>0.05026600000000001</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>4.023680104482519</v>
+        <v>3.502101293097096</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07723693372877748</v>
+        <v>0.0775461614814789</v>
       </c>
       <c r="C15">
-        <v>2882.105756212505</v>
+        <v>2830.012934810782</v>
       </c>
       <c r="D15">
-        <v>3077.318756212505</v>
+        <v>3058.226934810782</v>
       </c>
       <c r="E15">
-        <v>341.413</v>
+        <v>374.414</v>
       </c>
       <c r="F15">
-        <v>429.013</v>
+        <v>462.014</v>
       </c>
       <c r="G15">
         <v>233.8</v>
@@ -2517,45 +2517,45 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M15">
-        <v>26.2984969</v>
+        <v>29.6150974</v>
       </c>
       <c r="N15">
-        <v>65.80150309999996</v>
+        <v>62.48490259999996</v>
       </c>
       <c r="O15">
-        <v>11.84427055799999</v>
+        <v>11.24728246799999</v>
       </c>
       <c r="P15">
-        <v>53.95723254199997</v>
+        <v>51.23762013199997</v>
       </c>
       <c r="Q15">
-        <v>355.557232542</v>
+        <v>352.837620132</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08126707325146837</v>
+        <v>0.08161335055985917</v>
       </c>
       <c r="T15">
-        <v>0.5980258077835936</v>
+        <v>0.6038645406725266</v>
       </c>
       <c r="U15">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V15">
         <v>0.18</v>
       </c>
       <c r="W15">
-        <v>0.05026600000000001</v>
+        <v>0.052562</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y15">
-        <v>3.502101293097096</v>
+        <v>3.10990029024858</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0775461614814789</v>
+        <v>0.07851630923418029</v>
       </c>
       <c r="C16">
-        <v>2830.012934810782</v>
+        <v>2738.622796035477</v>
       </c>
       <c r="D16">
-        <v>3058.226934810782</v>
+        <v>2999.837796035477</v>
       </c>
       <c r="E16">
-        <v>374.414</v>
+        <v>407.4150000000001</v>
       </c>
       <c r="F16">
-        <v>462.014</v>
+        <v>495.015</v>
       </c>
       <c r="G16">
         <v>233.8</v>
@@ -2599,45 +2599,45 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M16">
-        <v>29.6150974</v>
+        <v>35.5915785</v>
       </c>
       <c r="N16">
-        <v>62.48490259999996</v>
+        <v>56.50842149999996</v>
       </c>
       <c r="O16">
-        <v>11.24728246799999</v>
+        <v>10.17151586999999</v>
       </c>
       <c r="P16">
-        <v>51.23762013199997</v>
+        <v>46.33690562999997</v>
       </c>
       <c r="Q16">
-        <v>352.837620132</v>
+        <v>347.93690563</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08161335055985917</v>
+        <v>0.08196777556962388</v>
       </c>
       <c r="T16">
-        <v>0.6038645406725266</v>
+        <v>0.6098406555117873</v>
       </c>
       <c r="U16">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V16">
         <v>0.18</v>
       </c>
       <c r="W16">
-        <v>0.052562</v>
+        <v>0.05895800000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>3.10990029024858</v>
+        <v>2.587690793202666</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07851630923418029</v>
+        <v>0.07910269698688173</v>
       </c>
       <c r="C17">
-        <v>2738.622796035477</v>
+        <v>2671.398326110399</v>
       </c>
       <c r="D17">
-        <v>2999.837796035477</v>
+        <v>2965.614326110399</v>
       </c>
       <c r="E17">
-        <v>407.415</v>
+        <v>440.4159999999999</v>
       </c>
       <c r="F17">
-        <v>495.015</v>
+        <v>528.016</v>
       </c>
       <c r="G17">
         <v>233.8</v>
@@ -2681,45 +2681,45 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M17">
-        <v>35.5915785</v>
+        <v>40.0236128</v>
       </c>
       <c r="N17">
-        <v>56.50842149999996</v>
+        <v>52.07638719999996</v>
       </c>
       <c r="O17">
-        <v>10.17151586999999</v>
+        <v>9.373749695999994</v>
       </c>
       <c r="P17">
-        <v>46.33690562999997</v>
+        <v>42.70263750399997</v>
       </c>
       <c r="Q17">
-        <v>347.93690563</v>
+        <v>344.302637504</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08196777556962388</v>
+        <v>0.08233063927009729</v>
       </c>
       <c r="T17">
-        <v>0.6098406555117873</v>
+        <v>0.615959058799602</v>
       </c>
       <c r="U17">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V17">
         <v>0.18</v>
       </c>
       <c r="W17">
-        <v>0.05895800000000001</v>
+        <v>0.06215600000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y17">
-        <v>2.587690793202666</v>
+        <v>2.301141590096533</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07910269698688173</v>
+        <v>0.07920938473958314</v>
       </c>
       <c r="C18">
-        <v>2671.398326110399</v>
+        <v>2632.25447339988</v>
       </c>
       <c r="D18">
-        <v>2965.614326110399</v>
+        <v>2959.47147339988</v>
       </c>
       <c r="E18">
-        <v>440.4159999999999</v>
+        <v>473.417</v>
       </c>
       <c r="F18">
-        <v>528.016</v>
+        <v>561.0170000000001</v>
       </c>
       <c r="G18">
         <v>233.8</v>
@@ -2763,28 +2763,28 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M18">
-        <v>40.0236128</v>
+        <v>42.52508860000001</v>
       </c>
       <c r="N18">
-        <v>52.07638719999996</v>
+        <v>49.57491139999996</v>
       </c>
       <c r="O18">
-        <v>9.373749695999994</v>
+        <v>8.923484051999992</v>
       </c>
       <c r="P18">
-        <v>42.70263750399997</v>
+        <v>40.65142734799996</v>
       </c>
       <c r="Q18">
-        <v>344.302637504</v>
+        <v>342.251427348</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08233063927009729</v>
+        <v>0.08270224667419654</v>
       </c>
       <c r="T18">
-        <v>0.615959058799602</v>
+        <v>0.6222248934919422</v>
       </c>
       <c r="U18">
         <v>0.07580000000000001</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>2.301141590096533</v>
+        <v>2.165780320090854</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07920938473958314</v>
+        <v>0.07931607249228453</v>
       </c>
       <c r="C19">
-        <v>2632.25447339988</v>
+        <v>2593.136016195895</v>
       </c>
       <c r="D19">
-        <v>2959.47147339988</v>
+        <v>2953.354016195895</v>
       </c>
       <c r="E19">
-        <v>473.417</v>
+        <v>506.418</v>
       </c>
       <c r="F19">
-        <v>561.0170000000001</v>
+        <v>594.018</v>
       </c>
       <c r="G19">
         <v>233.8</v>
@@ -2845,28 +2845,28 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M19">
-        <v>42.52508860000001</v>
+        <v>45.02656440000001</v>
       </c>
       <c r="N19">
-        <v>49.57491139999996</v>
+        <v>47.07343559999996</v>
       </c>
       <c r="O19">
-        <v>8.923484051999992</v>
+        <v>8.473218407999992</v>
       </c>
       <c r="P19">
-        <v>40.65142734799996</v>
+        <v>38.60021719199997</v>
       </c>
       <c r="Q19">
-        <v>342.251427348</v>
+        <v>340.200217192</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08270224667419654</v>
+        <v>0.08308291767351773</v>
       </c>
       <c r="T19">
-        <v>0.6222248934919422</v>
+        <v>0.6286435534206811</v>
       </c>
       <c r="U19">
         <v>0.07580000000000001</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>2.165780320090854</v>
+        <v>2.045459191196918</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07931607249228453</v>
+        <v>0.08163512024498597</v>
       </c>
       <c r="C20">
-        <v>2593.136016195895</v>
+        <v>2433.142084042146</v>
       </c>
       <c r="D20">
-        <v>2953.354016195895</v>
+        <v>2826.361084042146</v>
       </c>
       <c r="E20">
-        <v>506.4179999999999</v>
+        <v>539.419</v>
       </c>
       <c r="F20">
-        <v>594.0179999999999</v>
+        <v>627.019</v>
       </c>
       <c r="G20">
         <v>233.8</v>
@@ -2927,45 +2927,45 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M20">
-        <v>45.0265644</v>
+        <v>56.43171</v>
       </c>
       <c r="N20">
-        <v>47.07343559999997</v>
+        <v>35.66828999999997</v>
       </c>
       <c r="O20">
-        <v>8.473218407999994</v>
+        <v>6.420292199999994</v>
       </c>
       <c r="P20">
-        <v>38.60021719199997</v>
+        <v>29.24799779999998</v>
       </c>
       <c r="Q20">
-        <v>340.200217192</v>
+        <v>330.8479978</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08308291767351772</v>
+        <v>0.08347298795677278</v>
       </c>
       <c r="T20">
-        <v>0.628643553420681</v>
+        <v>0.6352206987797592</v>
       </c>
       <c r="U20">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V20">
         <v>0.18</v>
       </c>
       <c r="W20">
-        <v>0.06215600000000001</v>
+        <v>0.0738</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>2.045459191196919</v>
+        <v>1.632061123081331</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08163512024498597</v>
+        <v>0.08185824799768737</v>
       </c>
       <c r="C21">
-        <v>2433.142084042146</v>
+        <v>2388.496002759905</v>
       </c>
       <c r="D21">
-        <v>2826.361084042146</v>
+        <v>2814.716002759905</v>
       </c>
       <c r="E21">
-        <v>539.419</v>
+        <v>572.42</v>
       </c>
       <c r="F21">
-        <v>627.019</v>
+        <v>660.02</v>
       </c>
       <c r="G21">
         <v>233.8</v>
@@ -3009,28 +3009,28 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M21">
-        <v>56.43171</v>
+        <v>59.40179999999999</v>
       </c>
       <c r="N21">
-        <v>35.66828999999997</v>
+        <v>32.69819999999997</v>
       </c>
       <c r="O21">
-        <v>6.420292199999994</v>
+        <v>5.885675999999995</v>
       </c>
       <c r="P21">
-        <v>29.24799779999998</v>
+        <v>26.81252399999997</v>
       </c>
       <c r="Q21">
-        <v>330.8479978</v>
+        <v>328.412524</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08347298795677278</v>
+        <v>0.08387280999710921</v>
       </c>
       <c r="T21">
-        <v>0.6352206987797592</v>
+        <v>0.6419622727728141</v>
       </c>
       <c r="U21">
         <v>0.09</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>1.632061123081331</v>
+        <v>1.550458066927265</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08185824799768737</v>
+        <v>0.09250100674758402</v>
       </c>
       <c r="C22">
-        <v>2388.496002759905</v>
+        <v>1893.189898319524</v>
       </c>
       <c r="D22">
-        <v>2814.716002759905</v>
+        <v>2352.410898319524</v>
       </c>
       <c r="E22">
-        <v>572.42</v>
+        <v>605.421</v>
       </c>
       <c r="F22">
-        <v>660.02</v>
+        <v>693.0210000000001</v>
       </c>
       <c r="G22">
         <v>233.8</v>
@@ -3091,45 +3091,45 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M22">
-        <v>59.40179999999999</v>
+        <v>101.7354828</v>
       </c>
       <c r="N22">
-        <v>32.69819999999997</v>
+        <v>-9.635482800000048</v>
       </c>
       <c r="O22">
-        <v>5.885675999999995</v>
+        <v>-1.734386904000009</v>
       </c>
       <c r="P22">
-        <v>26.81252399999997</v>
+        <v>-7.901095896000039</v>
       </c>
       <c r="Q22">
-        <v>328.412524</v>
+        <v>293.698904104</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08387280999710921</v>
+        <v>0.08442593782839031</v>
       </c>
       <c r="T22">
-        <v>0.6419622727728141</v>
+        <v>0.6512888026436082</v>
       </c>
       <c r="U22">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V22">
-        <v>0.18</v>
+        <v>0.1629519961348234</v>
       </c>
       <c r="W22">
-        <v>0.0738</v>
+        <v>0.1228786469674079</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y22">
-        <v>1.550458066927265</v>
+        <v>0.9052888674156855</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09250100674758402</v>
+        <v>0.093511006747584</v>
       </c>
       <c r="C23">
-        <v>1893.189898319524</v>
+        <v>1824.084731123424</v>
       </c>
       <c r="D23">
-        <v>2352.410898319524</v>
+        <v>2316.306731123424</v>
       </c>
       <c r="E23">
-        <v>605.4209999999999</v>
+        <v>638.4219999999999</v>
       </c>
       <c r="F23">
-        <v>693.021</v>
+        <v>726.0219999999999</v>
       </c>
       <c r="G23">
         <v>233.8</v>
@@ -3173,37 +3173,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M23">
-        <v>101.7354828</v>
+        <v>106.5800296</v>
       </c>
       <c r="N23">
-        <v>-9.635482800000034</v>
+        <v>-14.48002960000004</v>
       </c>
       <c r="O23">
-        <v>-1.734386904000006</v>
+        <v>-2.606405328000007</v>
       </c>
       <c r="P23">
-        <v>-7.901095896000028</v>
+        <v>-11.87362427200003</v>
       </c>
       <c r="Q23">
-        <v>293.698904104</v>
+        <v>289.726375728</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08442593782839031</v>
+        <v>0.0849211421595235</v>
       </c>
       <c r="T23">
-        <v>0.6512888026436082</v>
+        <v>0.6596386590877569</v>
       </c>
       <c r="U23">
         <v>0.1468</v>
       </c>
       <c r="V23">
-        <v>0.1629519961348234</v>
+        <v>0.1555450872196042</v>
       </c>
       <c r="W23">
-        <v>0.1228786469674079</v>
+        <v>0.1239659811961621</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.9052888674156856</v>
+        <v>0.8641393734422453</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.093511006747584</v>
+        <v>0.094521006747584</v>
       </c>
       <c r="C24">
-        <v>1824.084731123424</v>
+        <v>1756.071046168941</v>
       </c>
       <c r="D24">
-        <v>2316.306731123424</v>
+        <v>2281.294046168941</v>
       </c>
       <c r="E24">
-        <v>638.4219999999999</v>
+        <v>671.423</v>
       </c>
       <c r="F24">
-        <v>726.0219999999999</v>
+        <v>759.023</v>
       </c>
       <c r="G24">
         <v>233.8</v>
@@ -3255,37 +3255,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M24">
-        <v>106.5800296</v>
+        <v>111.4245764</v>
       </c>
       <c r="N24">
-        <v>-14.48002960000004</v>
+        <v>-19.32457640000005</v>
       </c>
       <c r="O24">
-        <v>-2.606405328000007</v>
+        <v>-3.47842375200001</v>
       </c>
       <c r="P24">
-        <v>-11.87362427200003</v>
+        <v>-15.84615264800004</v>
       </c>
       <c r="Q24">
-        <v>289.726375728</v>
+        <v>285.753847352</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0849211421595235</v>
+        <v>0.08542920894081601</v>
       </c>
       <c r="T24">
-        <v>0.6596386590877569</v>
+        <v>0.6682053949200655</v>
       </c>
       <c r="U24">
         <v>0.1468</v>
       </c>
       <c r="V24">
-        <v>0.1555450872196042</v>
+        <v>0.1487822573404909</v>
       </c>
       <c r="W24">
-        <v>0.1239659811961621</v>
+        <v>0.124958764622416</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.8641393734422453</v>
+        <v>0.8265680963360607</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.094521006747584</v>
+        <v>0.1087817682575365</v>
       </c>
       <c r="C25">
-        <v>1756.071046168941</v>
+        <v>1321.817252753081</v>
       </c>
       <c r="D25">
-        <v>2281.294046168941</v>
+        <v>1880.041252753081</v>
       </c>
       <c r="E25">
-        <v>671.423</v>
+        <v>704.424</v>
       </c>
       <c r="F25">
-        <v>759.023</v>
+        <v>792.024</v>
       </c>
       <c r="G25">
         <v>233.8</v>
@@ -3337,45 +3337,45 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M25">
-        <v>111.4245764</v>
+        <v>159.0384192</v>
       </c>
       <c r="N25">
-        <v>-19.32457640000005</v>
+        <v>-66.93841920000003</v>
       </c>
       <c r="O25">
-        <v>-3.47842375200001</v>
+        <v>-12.048915456</v>
       </c>
       <c r="P25">
-        <v>-15.84615264800004</v>
+        <v>-54.88950374400002</v>
       </c>
       <c r="Q25">
-        <v>285.753847352</v>
+        <v>246.710496256</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08542920894081601</v>
+        <v>0.08633322683471162</v>
       </c>
       <c r="T25">
-        <v>0.6682053949200655</v>
+        <v>0.6834484353427864</v>
       </c>
       <c r="U25">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.1487822573404909</v>
+        <v>0.1042389636629386</v>
       </c>
       <c r="W25">
-        <v>0.124958764622416</v>
+        <v>0.1798688160964819</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y25">
-        <v>0.8265680963360607</v>
+        <v>0.5791053536829922</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1087817682575365</v>
+        <v>0.1103317682575365</v>
       </c>
       <c r="C26">
-        <v>1321.817252753081</v>
+        <v>1253.549213408381</v>
       </c>
       <c r="D26">
-        <v>1880.041252753081</v>
+        <v>1844.774213408381</v>
       </c>
       <c r="E26">
-        <v>704.424</v>
+        <v>737.425</v>
       </c>
       <c r="F26">
-        <v>792.024</v>
+        <v>825.025</v>
       </c>
       <c r="G26">
         <v>233.8</v>
@@ -3419,37 +3419,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M26">
-        <v>159.0384192</v>
+        <v>165.66502</v>
       </c>
       <c r="N26">
-        <v>-66.93841920000003</v>
+        <v>-73.56502000000003</v>
       </c>
       <c r="O26">
-        <v>-12.048915456</v>
+        <v>-13.2417036</v>
       </c>
       <c r="P26">
-        <v>-54.88950374400002</v>
+        <v>-60.32331640000002</v>
       </c>
       <c r="Q26">
-        <v>246.710496256</v>
+        <v>241.2766836</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08633322683471162</v>
+        <v>0.08687366985917444</v>
       </c>
       <c r="T26">
-        <v>0.6834484353427864</v>
+        <v>0.6925610811473569</v>
       </c>
       <c r="U26">
         <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.1042389636629386</v>
+        <v>0.100069405116421</v>
       </c>
       <c r="W26">
-        <v>0.1798688160964819</v>
+        <v>0.1807060634526227</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.5791053536829922</v>
+        <v>0.5559411395356724</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1103317682575365</v>
+        <v>0.1118817682575365</v>
       </c>
       <c r="C27">
-        <v>1253.549213408381</v>
+        <v>1186.579935280632</v>
       </c>
       <c r="D27">
-        <v>1844.774213408381</v>
+        <v>1810.805935280632</v>
       </c>
       <c r="E27">
-        <v>737.425</v>
+        <v>770.4259999999999</v>
       </c>
       <c r="F27">
-        <v>825.025</v>
+        <v>858.026</v>
       </c>
       <c r="G27">
         <v>233.8</v>
@@ -3501,37 +3501,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M27">
-        <v>165.66502</v>
+        <v>172.2916208</v>
       </c>
       <c r="N27">
-        <v>-73.56502000000003</v>
+        <v>-80.19162080000004</v>
       </c>
       <c r="O27">
-        <v>-13.2417036</v>
+        <v>-14.43449174400001</v>
       </c>
       <c r="P27">
-        <v>-60.32331640000002</v>
+        <v>-65.75712905600003</v>
       </c>
       <c r="Q27">
-        <v>241.2766836</v>
+        <v>235.842870944</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08687366985917444</v>
+        <v>0.08742871945186598</v>
       </c>
       <c r="T27">
-        <v>0.6925610811473569</v>
+        <v>0.7019200146763753</v>
       </c>
       <c r="U27">
         <v>0.2008</v>
       </c>
       <c r="V27">
-        <v>0.100069405116421</v>
+        <v>0.09622058184271252</v>
       </c>
       <c r="W27">
-        <v>0.1807060634526227</v>
+        <v>0.1814789071659833</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.5559411395356724</v>
+        <v>0.5345587880150696</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1118817682575365</v>
+        <v>0.1134317682575365</v>
       </c>
       <c r="C28">
-        <v>1186.579935280632</v>
+        <v>1120.838972288311</v>
       </c>
       <c r="D28">
-        <v>1810.805935280632</v>
+        <v>1778.065972288311</v>
       </c>
       <c r="E28">
-        <v>770.4259999999999</v>
+        <v>803.427</v>
       </c>
       <c r="F28">
-        <v>858.026</v>
+        <v>891.027</v>
       </c>
       <c r="G28">
         <v>233.8</v>
@@ -3583,37 +3583,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M28">
-        <v>172.2916208</v>
+        <v>178.9182216</v>
       </c>
       <c r="N28">
-        <v>-80.19162080000004</v>
+        <v>-86.81822160000004</v>
       </c>
       <c r="O28">
-        <v>-14.43449174400001</v>
+        <v>-15.62727988800001</v>
       </c>
       <c r="P28">
-        <v>-65.75712905600003</v>
+        <v>-71.19094171200004</v>
       </c>
       <c r="Q28">
-        <v>235.842870944</v>
+        <v>230.409058288</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08742871945186598</v>
+        <v>0.08799897588271346</v>
       </c>
       <c r="T28">
-        <v>0.7019200146763753</v>
+        <v>0.711535357343175</v>
       </c>
       <c r="U28">
         <v>0.2008</v>
       </c>
       <c r="V28">
-        <v>0.09622058184271252</v>
+        <v>0.09265685658927873</v>
       </c>
       <c r="W28">
-        <v>0.1814789071659833</v>
+        <v>0.1821945031968728</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.5345587880150696</v>
+        <v>0.5147603143848818</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1134317682575365</v>
+        <v>0.1248990940388119</v>
       </c>
       <c r="C29">
-        <v>1120.838972288311</v>
+        <v>878.0588651641351</v>
       </c>
       <c r="D29">
-        <v>1778.065972288311</v>
+        <v>1568.286865164135</v>
       </c>
       <c r="E29">
-        <v>803.427</v>
+        <v>836.428</v>
       </c>
       <c r="F29">
-        <v>891.027</v>
+        <v>924.028</v>
       </c>
       <c r="G29">
         <v>233.8</v>
@@ -3665,45 +3665,45 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M29">
-        <v>178.9182216</v>
+        <v>217.8858024</v>
       </c>
       <c r="N29">
-        <v>-86.81822160000004</v>
+        <v>-125.7858024000001</v>
       </c>
       <c r="O29">
-        <v>-15.62727988800001</v>
+        <v>-22.64144443200001</v>
       </c>
       <c r="P29">
-        <v>-71.19094171200004</v>
+        <v>-103.144357968</v>
       </c>
       <c r="Q29">
-        <v>230.409058288</v>
+        <v>198.455642032</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08799897588271346</v>
+        <v>0.08874802524396698</v>
       </c>
       <c r="T29">
-        <v>0.711535357343175</v>
+        <v>0.7241654056744078</v>
       </c>
       <c r="U29">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.09265685658927873</v>
+        <v>0.07608572847516563</v>
       </c>
       <c r="W29">
-        <v>0.1821945031968728</v>
+        <v>0.217858985225556</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y29">
-        <v>0.5147603143848818</v>
+        <v>0.422698491528698</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1248990940388119</v>
+        <v>0.1267990940388119</v>
       </c>
       <c r="C30">
-        <v>878.0588651641351</v>
+        <v>814.9885474848037</v>
       </c>
       <c r="D30">
-        <v>1568.286865164135</v>
+        <v>1538.217547484804</v>
       </c>
       <c r="E30">
-        <v>836.428</v>
+        <v>869.4290000000001</v>
       </c>
       <c r="F30">
-        <v>924.028</v>
+        <v>957.0290000000001</v>
       </c>
       <c r="G30">
         <v>233.8</v>
@@ -3747,37 +3747,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M30">
-        <v>217.8858024</v>
+        <v>225.6674382</v>
       </c>
       <c r="N30">
-        <v>-125.7858024000001</v>
+        <v>-133.5674382000001</v>
       </c>
       <c r="O30">
-        <v>-22.64144443200001</v>
+        <v>-24.04213887600001</v>
       </c>
       <c r="P30">
-        <v>-103.144357968</v>
+        <v>-109.5252993240001</v>
       </c>
       <c r="Q30">
-        <v>198.455642032</v>
+        <v>192.074700676</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08874802524396698</v>
+        <v>0.08935292700796651</v>
       </c>
       <c r="T30">
-        <v>0.7241654056744078</v>
+        <v>0.7343649184303854</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.07608572847516563</v>
+        <v>0.07346208266567715</v>
       </c>
       <c r="W30">
-        <v>0.217858985225556</v>
+        <v>0.2184776409074334</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.422698491528698</v>
+        <v>0.4081226814759842</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1267990940388119</v>
+        <v>0.1286990940388119</v>
       </c>
       <c r="C31">
-        <v>814.9885474848039</v>
+        <v>753.049596988089</v>
       </c>
       <c r="D31">
-        <v>1538.217547484804</v>
+        <v>1509.279596988089</v>
       </c>
       <c r="E31">
-        <v>869.4289999999999</v>
+        <v>902.4299999999999</v>
       </c>
       <c r="F31">
-        <v>957.0289999999999</v>
+        <v>990.03</v>
       </c>
       <c r="G31">
         <v>233.8</v>
@@ -3829,37 +3829,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M31">
-        <v>225.6674382</v>
+        <v>233.449074</v>
       </c>
       <c r="N31">
-        <v>-133.5674382</v>
+        <v>-141.349074</v>
       </c>
       <c r="O31">
-        <v>-24.042138876</v>
+        <v>-25.44283332000001</v>
       </c>
       <c r="P31">
-        <v>-109.525299324</v>
+        <v>-115.90624068</v>
       </c>
       <c r="Q31">
-        <v>192.074700676</v>
+        <v>185.69375932</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08935292700796651</v>
+        <v>0.0899751116795089</v>
       </c>
       <c r="T31">
-        <v>0.7343649184303854</v>
+        <v>0.7448558458365339</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.07346208266567716</v>
+        <v>0.07101334657682126</v>
       </c>
       <c r="W31">
-        <v>0.2184776409074334</v>
+        <v>0.2190550528771856</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.4081226814759843</v>
+        <v>0.3945185920934515</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1286990940388119</v>
+        <v>0.1305990940388119</v>
       </c>
       <c r="C32">
-        <v>753.049596988089</v>
+        <v>692.179340670132</v>
       </c>
       <c r="D32">
-        <v>1509.279596988089</v>
+        <v>1481.410340670132</v>
       </c>
       <c r="E32">
-        <v>902.4299999999999</v>
+        <v>935.4309999999999</v>
       </c>
       <c r="F32">
-        <v>990.03</v>
+        <v>1023.031</v>
       </c>
       <c r="G32">
         <v>233.8</v>
@@ -3911,37 +3911,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M32">
-        <v>233.449074</v>
+        <v>241.2307098</v>
       </c>
       <c r="N32">
-        <v>-141.349074</v>
+        <v>-149.1307098</v>
       </c>
       <c r="O32">
-        <v>-25.44283332000001</v>
+        <v>-26.843527764</v>
       </c>
       <c r="P32">
-        <v>-115.90624068</v>
+        <v>-122.287182036</v>
       </c>
       <c r="Q32">
-        <v>185.69375932</v>
+        <v>179.312817964</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0899751116795089</v>
+        <v>0.09061533068935686</v>
       </c>
       <c r="T32">
-        <v>0.7448558458365339</v>
+        <v>0.7556508580950343</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.07101334657682126</v>
+        <v>0.06872259346143993</v>
       </c>
       <c r="W32">
-        <v>0.2190550528771856</v>
+        <v>0.2195952124617925</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3945185920934515</v>
+        <v>0.3817921858968886</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1305990940388119</v>
+        <v>0.1324990940388119</v>
       </c>
       <c r="C33">
-        <v>692.179340670132</v>
+        <v>632.3196506952395</v>
       </c>
       <c r="D33">
-        <v>1481.410340670132</v>
+        <v>1454.551650695239</v>
       </c>
       <c r="E33">
-        <v>935.4309999999999</v>
+        <v>968.4319999999999</v>
       </c>
       <c r="F33">
-        <v>1023.031</v>
+        <v>1056.032</v>
       </c>
       <c r="G33">
         <v>233.8</v>
@@ -3993,37 +3993,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M33">
-        <v>241.2307098</v>
+        <v>249.0123456</v>
       </c>
       <c r="N33">
-        <v>-149.1307098</v>
+        <v>-156.9123456</v>
       </c>
       <c r="O33">
-        <v>-26.843527764</v>
+        <v>-28.24422220800001</v>
       </c>
       <c r="P33">
-        <v>-122.287182036</v>
+        <v>-128.668123392</v>
       </c>
       <c r="Q33">
-        <v>179.312817964</v>
+        <v>172.931876608</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09061533068935686</v>
+        <v>0.09127437967008269</v>
       </c>
       <c r="T33">
-        <v>0.7556508580950343</v>
+        <v>0.7667633707140789</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.06872259346143993</v>
+        <v>0.06657501241576994</v>
       </c>
       <c r="W33">
-        <v>0.2195952124617925</v>
+        <v>0.2201016120723615</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3817921858968886</v>
+        <v>0.3698611800876107</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1324990940388119</v>
+        <v>0.1343990940388119</v>
       </c>
       <c r="C34">
-        <v>632.3196506952395</v>
+        <v>573.4165397026243</v>
       </c>
       <c r="D34">
-        <v>1454.551650695239</v>
+        <v>1428.649539702624</v>
       </c>
       <c r="E34">
-        <v>968.4319999999999</v>
+        <v>1001.433</v>
       </c>
       <c r="F34">
-        <v>1056.032</v>
+        <v>1089.033</v>
       </c>
       <c r="G34">
         <v>233.8</v>
@@ -4075,37 +4075,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M34">
-        <v>249.0123456</v>
+        <v>256.7939814000001</v>
       </c>
       <c r="N34">
-        <v>-156.9123456</v>
+        <v>-164.6939814000001</v>
       </c>
       <c r="O34">
-        <v>-28.24422220800001</v>
+        <v>-29.64491665200002</v>
       </c>
       <c r="P34">
-        <v>-128.668123392</v>
+        <v>-135.0490647480001</v>
       </c>
       <c r="Q34">
-        <v>172.931876608</v>
+        <v>166.5509352519999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09127437967008269</v>
+        <v>0.0919531017547108</v>
       </c>
       <c r="T34">
-        <v>0.7667633707140789</v>
+        <v>0.7782076001277219</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.06657501241576994</v>
+        <v>0.06455758779711021</v>
       </c>
       <c r="W34">
-        <v>0.2201016120723615</v>
+        <v>0.2205773207974414</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3698611800876107</v>
+        <v>0.3586532655395013</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1343990940388119</v>
+        <v>0.1362990940388119</v>
       </c>
       <c r="C35">
-        <v>573.4165397026243</v>
+        <v>515.4197985963724</v>
       </c>
       <c r="D35">
-        <v>1428.649539702624</v>
+        <v>1403.653798596373</v>
       </c>
       <c r="E35">
-        <v>1001.433</v>
+        <v>1034.434</v>
       </c>
       <c r="F35">
-        <v>1089.033</v>
+        <v>1122.034</v>
       </c>
       <c r="G35">
         <v>233.8</v>
@@ -4157,37 +4157,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M35">
-        <v>256.7939814000001</v>
+        <v>264.5756172</v>
       </c>
       <c r="N35">
-        <v>-164.6939814000001</v>
+        <v>-172.4756172</v>
       </c>
       <c r="O35">
-        <v>-29.64491665200002</v>
+        <v>-31.04561109600001</v>
       </c>
       <c r="P35">
-        <v>-135.0490647480001</v>
+        <v>-141.430006104</v>
       </c>
       <c r="Q35">
-        <v>166.5509352519999</v>
+        <v>160.169993896</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.0919531017547108</v>
+        <v>0.09265239117523671</v>
       </c>
       <c r="T35">
-        <v>0.7782076001277219</v>
+        <v>0.7899986243720812</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.06455758779711021</v>
+        <v>0.06265883521484229</v>
       </c>
       <c r="W35">
-        <v>0.2205773207974414</v>
+        <v>0.2210250466563402</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3586532655395013</v>
+        <v>0.3481046400824571</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1362990940388119</v>
+        <v>0.1381990940388119</v>
       </c>
       <c r="C36">
-        <v>515.4197985963724</v>
+        <v>458.2826717050871</v>
       </c>
       <c r="D36">
-        <v>1403.653798596373</v>
+        <v>1379.517671705087</v>
       </c>
       <c r="E36">
-        <v>1034.434</v>
+        <v>1067.435</v>
       </c>
       <c r="F36">
-        <v>1122.034</v>
+        <v>1155.035</v>
       </c>
       <c r="G36">
         <v>233.8</v>
@@ -4239,37 +4239,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M36">
-        <v>264.5756172</v>
+        <v>272.357253</v>
       </c>
       <c r="N36">
-        <v>-172.4756172</v>
+        <v>-180.257253</v>
       </c>
       <c r="O36">
-        <v>-31.04561109600001</v>
+        <v>-32.44630554</v>
       </c>
       <c r="P36">
-        <v>-141.430006104</v>
+        <v>-147.8109474600001</v>
       </c>
       <c r="Q36">
-        <v>160.169993896</v>
+        <v>153.78905254</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09265239117523671</v>
+        <v>0.09337319719331727</v>
       </c>
       <c r="T36">
-        <v>0.7899986243720812</v>
+        <v>0.802152449362421</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.06265883521484229</v>
+        <v>0.0608685827801325</v>
       </c>
       <c r="W36">
-        <v>0.2210250466563402</v>
+        <v>0.2214471881804448</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3481046400824571</v>
+        <v>0.3381587932229584</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1381990940388119</v>
+        <v>0.1400990940388119</v>
       </c>
       <c r="C37">
-        <v>458.2826717050871</v>
+        <v>401.9615648891825</v>
       </c>
       <c r="D37">
-        <v>1379.517671705087</v>
+        <v>1356.197564889183</v>
       </c>
       <c r="E37">
-        <v>1067.435</v>
+        <v>1100.436</v>
       </c>
       <c r="F37">
-        <v>1155.035</v>
+        <v>1188.036</v>
       </c>
       <c r="G37">
         <v>233.8</v>
@@ -4321,37 +4321,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M37">
-        <v>272.357253</v>
+        <v>280.1388888</v>
       </c>
       <c r="N37">
-        <v>-180.257253</v>
+        <v>-188.0388888000001</v>
       </c>
       <c r="O37">
-        <v>-32.44630554</v>
+        <v>-33.84699998400001</v>
       </c>
       <c r="P37">
-        <v>-147.8109474600001</v>
+        <v>-154.191888816</v>
       </c>
       <c r="Q37">
-        <v>153.78905254</v>
+        <v>147.408111184</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09337319719331727</v>
+        <v>0.09411652839946286</v>
       </c>
       <c r="T37">
-        <v>0.802152449362421</v>
+        <v>0.8146860813837088</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.0608685827801325</v>
+        <v>0.05917778881401772</v>
       </c>
       <c r="W37">
-        <v>0.2214471881804448</v>
+        <v>0.2218458773976546</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3381587932229584</v>
+        <v>0.3287654934112095</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1400990940388119</v>
+        <v>0.1419990940388119</v>
       </c>
       <c r="C38">
-        <v>401.9615648891825</v>
+        <v>346.4157827618938</v>
       </c>
       <c r="D38">
-        <v>1356.197564889182</v>
+        <v>1333.652782761894</v>
       </c>
       <c r="E38">
-        <v>1100.436</v>
+        <v>1133.437</v>
       </c>
       <c r="F38">
-        <v>1188.036</v>
+        <v>1221.037</v>
       </c>
       <c r="G38">
         <v>233.8</v>
@@ -4403,37 +4403,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M38">
-        <v>280.1388888</v>
+        <v>287.9205246</v>
       </c>
       <c r="N38">
-        <v>-188.0388888</v>
+        <v>-195.8205246000001</v>
       </c>
       <c r="O38">
-        <v>-33.846999984</v>
+        <v>-35.24769442800001</v>
       </c>
       <c r="P38">
-        <v>-154.191888816</v>
+        <v>-160.572830172</v>
       </c>
       <c r="Q38">
-        <v>147.408111184</v>
+        <v>141.027169828</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09411652839946286</v>
+        <v>0.09488345742167656</v>
       </c>
       <c r="T38">
-        <v>0.8146860813837088</v>
+        <v>0.8276176064850375</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.05917778881401772</v>
+        <v>0.05757838911634156</v>
       </c>
       <c r="W38">
-        <v>0.2218458773976546</v>
+        <v>0.2222230158463667</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3287654934112096</v>
+        <v>0.3198799395352309</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1419990940388119</v>
+        <v>0.1438990940388119</v>
       </c>
       <c r="C39">
-        <v>346.4157827618938</v>
+        <v>291.6072916915839</v>
       </c>
       <c r="D39">
-        <v>1333.652782761894</v>
+        <v>1311.845291691584</v>
       </c>
       <c r="E39">
-        <v>1133.437</v>
+        <v>1166.438</v>
       </c>
       <c r="F39">
-        <v>1221.037</v>
+        <v>1254.038</v>
       </c>
       <c r="G39">
         <v>233.8</v>
@@ -4485,37 +4485,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M39">
-        <v>287.9205246</v>
+        <v>295.7021604</v>
       </c>
       <c r="N39">
-        <v>-195.8205246000001</v>
+        <v>-203.6021604000001</v>
       </c>
       <c r="O39">
-        <v>-35.24769442800001</v>
+        <v>-36.64838887200001</v>
       </c>
       <c r="P39">
-        <v>-160.572830172</v>
+        <v>-166.9537715280001</v>
       </c>
       <c r="Q39">
-        <v>141.027169828</v>
+        <v>134.646228472</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09488345742167656</v>
+        <v>0.09567512608976811</v>
       </c>
       <c r="T39">
-        <v>0.8276176064850375</v>
+        <v>0.8409662775573769</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.05757838911634156</v>
+        <v>0.05606316835012205</v>
       </c>
       <c r="W39">
-        <v>0.2222230158463667</v>
+        <v>0.2225803049030412</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3198799395352309</v>
+        <v>0.3114620463895669</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1438990940388119</v>
+        <v>0.1457990940388119</v>
       </c>
       <c r="C40">
-        <v>291.6072916915839</v>
+        <v>237.5005056818541</v>
       </c>
       <c r="D40">
-        <v>1311.845291691584</v>
+        <v>1290.739505681854</v>
       </c>
       <c r="E40">
-        <v>1166.438</v>
+        <v>1199.439</v>
       </c>
       <c r="F40">
-        <v>1254.038</v>
+        <v>1287.039</v>
       </c>
       <c r="G40">
         <v>233.8</v>
@@ -4567,37 +4567,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M40">
-        <v>295.7021604</v>
+        <v>303.4837962</v>
       </c>
       <c r="N40">
-        <v>-203.6021604000001</v>
+        <v>-211.3837962000001</v>
       </c>
       <c r="O40">
-        <v>-36.64838887200001</v>
+        <v>-38.04908331600001</v>
       </c>
       <c r="P40">
-        <v>-166.9537715280001</v>
+        <v>-173.3347128840001</v>
       </c>
       <c r="Q40">
-        <v>134.646228472</v>
+        <v>128.265287116</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09567512608976811</v>
+        <v>0.09649275110763317</v>
       </c>
       <c r="T40">
-        <v>0.8409662775573769</v>
+        <v>0.8547526099763503</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.05606316835012205</v>
+        <v>0.05462565121293943</v>
       </c>
       <c r="W40">
-        <v>0.2225803049030412</v>
+        <v>0.2229192714439889</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3114620463895669</v>
+        <v>0.3034758400718857</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1457990940388119</v>
+        <v>0.1476990940388119</v>
       </c>
       <c r="C41">
-        <v>237.5005056818541</v>
+        <v>184.062092593743</v>
       </c>
       <c r="D41">
-        <v>1290.739505681854</v>
+        <v>1270.302092593743</v>
       </c>
       <c r="E41">
-        <v>1199.439</v>
+        <v>1232.44</v>
       </c>
       <c r="F41">
-        <v>1287.039</v>
+        <v>1320.04</v>
       </c>
       <c r="G41">
         <v>233.8</v>
@@ -4649,37 +4649,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M41">
-        <v>303.4837962</v>
+        <v>311.265432</v>
       </c>
       <c r="N41">
-        <v>-211.3837962000001</v>
+        <v>-219.165432</v>
       </c>
       <c r="O41">
-        <v>-38.04908331600001</v>
+        <v>-39.44977776</v>
       </c>
       <c r="P41">
-        <v>-173.3347128840001</v>
+        <v>-179.71565424</v>
       </c>
       <c r="Q41">
-        <v>128.265287116</v>
+        <v>121.88434576</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09649275110763317</v>
+        <v>0.09733763029276038</v>
       </c>
       <c r="T41">
-        <v>0.8547526099763503</v>
+        <v>0.8689984868092895</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.05462565121293943</v>
+        <v>0.05326000993261595</v>
       </c>
       <c r="W41">
-        <v>0.2229192714439889</v>
+        <v>0.2232412896578892</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3034758400718857</v>
+        <v>0.2958889440700886</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1476990940388119</v>
+        <v>0.1495990940388119</v>
       </c>
       <c r="C42">
-        <v>184.062092593743</v>
+        <v>131.2607984904982</v>
       </c>
       <c r="D42">
-        <v>1270.302092593743</v>
+        <v>1250.501798490498</v>
       </c>
       <c r="E42">
-        <v>1232.44</v>
+        <v>1265.441</v>
       </c>
       <c r="F42">
-        <v>1320.04</v>
+        <v>1353.041</v>
       </c>
       <c r="G42">
         <v>233.8</v>
@@ -4731,37 +4731,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M42">
-        <v>311.265432</v>
+        <v>319.0470678</v>
       </c>
       <c r="N42">
-        <v>-219.165432</v>
+        <v>-226.9470678000001</v>
       </c>
       <c r="O42">
-        <v>-39.44977776</v>
+        <v>-40.85047220400001</v>
       </c>
       <c r="P42">
-        <v>-179.71565424</v>
+        <v>-186.096595596</v>
       </c>
       <c r="Q42">
-        <v>121.88434576</v>
+        <v>115.503404404</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09733763029276038</v>
+        <v>0.0982111494502648</v>
       </c>
       <c r="T42">
-        <v>0.8689984868092895</v>
+        <v>0.8837272747213113</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.05326000993261595</v>
+        <v>0.05196098530011311</v>
       </c>
       <c r="W42">
-        <v>0.2232412896578892</v>
+        <v>0.2235475996662334</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2958889440700886</v>
+        <v>0.288672140556184</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1495990940388119</v>
+        <v>0.1514990940388119</v>
       </c>
       <c r="C43">
-        <v>131.2607984904982</v>
+        <v>79.06728815793417</v>
       </c>
       <c r="D43">
-        <v>1250.501798490498</v>
+        <v>1231.309288157934</v>
       </c>
       <c r="E43">
-        <v>1265.441</v>
+        <v>1298.442</v>
       </c>
       <c r="F43">
-        <v>1353.041</v>
+        <v>1386.042</v>
       </c>
       <c r="G43">
         <v>233.8</v>
@@ -4813,37 +4813,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M43">
-        <v>319.0470678</v>
+        <v>326.8287036</v>
       </c>
       <c r="N43">
-        <v>-226.9470678000001</v>
+        <v>-234.7287036000001</v>
       </c>
       <c r="O43">
-        <v>-40.85047220400001</v>
+        <v>-42.25116664800001</v>
       </c>
       <c r="P43">
-        <v>-186.096595596</v>
+        <v>-192.4775369520001</v>
       </c>
       <c r="Q43">
-        <v>115.503404404</v>
+        <v>109.122463048</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.0982111494502648</v>
+        <v>0.09911478995802797</v>
       </c>
       <c r="T43">
-        <v>0.8837272747213113</v>
+        <v>0.8989639518716787</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.05196098530011311</v>
+        <v>0.05072381898344375</v>
       </c>
       <c r="W43">
-        <v>0.2235475996662334</v>
+        <v>0.223839323483704</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.288672140556184</v>
+        <v>0.2817989943524652</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1514990940388119</v>
+        <v>0.1533990940388119</v>
       </c>
       <c r="C44">
-        <v>79.0672881579344</v>
+        <v>27.45400008880142</v>
       </c>
       <c r="D44">
-        <v>1231.309288157934</v>
+        <v>1212.697000088801</v>
       </c>
       <c r="E44">
-        <v>1298.442</v>
+        <v>1331.443</v>
       </c>
       <c r="F44">
-        <v>1386.042</v>
+        <v>1419.043</v>
       </c>
       <c r="G44">
         <v>233.8</v>
@@ -4895,37 +4895,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M44">
-        <v>326.8287036</v>
+        <v>334.6103394</v>
       </c>
       <c r="N44">
-        <v>-234.7287036</v>
+        <v>-242.5103394</v>
       </c>
       <c r="O44">
-        <v>-42.251166648</v>
+        <v>-43.651861092</v>
       </c>
       <c r="P44">
-        <v>-192.477536952</v>
+        <v>-198.858478308</v>
       </c>
       <c r="Q44">
-        <v>109.122463048</v>
+        <v>102.741521692</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09911478995802797</v>
+        <v>0.1000501371502741</v>
       </c>
       <c r="T44">
-        <v>0.8989639518716787</v>
+        <v>0.9147352492729361</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.05072381898344376</v>
+        <v>0.04954419528615437</v>
       </c>
       <c r="W44">
-        <v>0.223839323483704</v>
+        <v>0.2241174787515248</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2817989943524654</v>
+        <v>0.2752455293675243</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1533990940388119</v>
+        <v>0.1552990940388119</v>
       </c>
       <c r="C45">
-        <v>27.45400008880142</v>
+        <v>-23.60498557647315</v>
       </c>
       <c r="D45">
-        <v>1212.697000088801</v>
+        <v>1194.639014423527</v>
       </c>
       <c r="E45">
-        <v>1331.443</v>
+        <v>1364.444</v>
       </c>
       <c r="F45">
-        <v>1419.043</v>
+        <v>1452.044</v>
       </c>
       <c r="G45">
         <v>233.8</v>
@@ -4977,37 +4977,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M45">
-        <v>334.6103394</v>
+        <v>342.3919752</v>
       </c>
       <c r="N45">
-        <v>-242.5103394</v>
+        <v>-250.2919752</v>
       </c>
       <c r="O45">
-        <v>-43.651861092</v>
+        <v>-45.052555536</v>
       </c>
       <c r="P45">
-        <v>-198.858478308</v>
+        <v>-205.239419664</v>
       </c>
       <c r="Q45">
-        <v>102.741521692</v>
+        <v>96.360580336</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1000501371502741</v>
+        <v>0.1010188895993861</v>
       </c>
       <c r="T45">
-        <v>0.9147352492729361</v>
+        <v>0.9310698072956672</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.04954419528615437</v>
+        <v>0.04841819084783268</v>
       </c>
       <c r="W45">
-        <v>0.2241174787515248</v>
+        <v>0.2243829905980811</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2752455293675243</v>
+        <v>0.268989949154626</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1552990940388119</v>
+        <v>0.1571990940388119</v>
       </c>
       <c r="C46">
-        <v>-23.60498557647315</v>
+        <v>-74.13406748338571</v>
       </c>
       <c r="D46">
-        <v>1194.639014423527</v>
+        <v>1177.110932516614</v>
       </c>
       <c r="E46">
-        <v>1364.444</v>
+        <v>1397.445</v>
       </c>
       <c r="F46">
-        <v>1452.044</v>
+        <v>1485.045</v>
       </c>
       <c r="G46">
         <v>233.8</v>
@@ -5059,37 +5059,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M46">
-        <v>342.3919752</v>
+        <v>350.1736110000001</v>
       </c>
       <c r="N46">
-        <v>-250.2919752</v>
+        <v>-258.0736110000001</v>
       </c>
       <c r="O46">
-        <v>-45.052555536</v>
+        <v>-46.45324998000002</v>
       </c>
       <c r="P46">
-        <v>-205.239419664</v>
+        <v>-211.6203610200001</v>
       </c>
       <c r="Q46">
-        <v>96.360580336</v>
+        <v>89.97963897999995</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1010188895993861</v>
+        <v>0.102022869410284</v>
       </c>
       <c r="T46">
-        <v>0.9310698072956672</v>
+        <v>0.9479983492464975</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.04841819084783268</v>
+        <v>0.04734223105121416</v>
       </c>
       <c r="W46">
-        <v>0.2243829905980811</v>
+        <v>0.2246367019181237</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.268989949154626</v>
+        <v>0.2630123947289676</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1571990940388119</v>
+        <v>0.1590990940388119</v>
       </c>
       <c r="C47">
-        <v>-74.13406748338571</v>
+        <v>-124.1562330480454</v>
       </c>
       <c r="D47">
-        <v>1177.110932516614</v>
+        <v>1160.089766951955</v>
       </c>
       <c r="E47">
-        <v>1397.445</v>
+        <v>1430.446</v>
       </c>
       <c r="F47">
-        <v>1485.045</v>
+        <v>1518.046</v>
       </c>
       <c r="G47">
         <v>233.8</v>
@@ -5141,37 +5141,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M47">
-        <v>350.1736110000001</v>
+        <v>357.9552468000001</v>
       </c>
       <c r="N47">
-        <v>-258.0736110000001</v>
+        <v>-265.8552468000001</v>
       </c>
       <c r="O47">
-        <v>-46.45324998000002</v>
+        <v>-47.85394442400001</v>
       </c>
       <c r="P47">
-        <v>-211.6203610200001</v>
+        <v>-218.0013023760001</v>
       </c>
       <c r="Q47">
-        <v>89.97963897999995</v>
+        <v>83.59869762399995</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.102022869410284</v>
+        <v>0.1030640336586227</v>
       </c>
       <c r="T47">
-        <v>0.9479983492464975</v>
+        <v>0.9655538742325438</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.04734223105121416</v>
+        <v>0.04631305211531821</v>
       </c>
       <c r="W47">
-        <v>0.2246367019181237</v>
+        <v>0.224879382311208</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2630123947289676</v>
+        <v>0.2572947339739901</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1590990940388119</v>
+        <v>0.1609990940388119</v>
       </c>
       <c r="C48">
-        <v>-124.1562330480454</v>
+        <v>-173.6931590355341</v>
       </c>
       <c r="D48">
-        <v>1160.089766951955</v>
+        <v>1143.553840964466</v>
       </c>
       <c r="E48">
-        <v>1430.446</v>
+        <v>1463.447</v>
       </c>
       <c r="F48">
-        <v>1518.046</v>
+        <v>1551.047</v>
       </c>
       <c r="G48">
         <v>233.8</v>
@@ -5223,37 +5223,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M48">
-        <v>357.9552468000001</v>
+        <v>365.7368826</v>
       </c>
       <c r="N48">
-        <v>-265.8552468000001</v>
+        <v>-273.6368826</v>
       </c>
       <c r="O48">
-        <v>-47.85394442400001</v>
+        <v>-49.25463886800001</v>
       </c>
       <c r="P48">
-        <v>-218.0013023760001</v>
+        <v>-224.382243732</v>
       </c>
       <c r="Q48">
-        <v>83.59869762399995</v>
+        <v>77.21775626799999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1030640336586227</v>
+        <v>0.1041444871238797</v>
       </c>
       <c r="T48">
-        <v>0.9655538742325438</v>
+        <v>0.9837718718595728</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.04631305211531821</v>
+        <v>0.04532766802775826</v>
       </c>
       <c r="W48">
-        <v>0.224879382311208</v>
+        <v>0.2251117358790546</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2572947339739901</v>
+        <v>0.2518203779319903</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1609990940388119</v>
+        <v>0.1628990940388119</v>
       </c>
       <c r="C49">
-        <v>-173.6931590355341</v>
+        <v>-222.7653036572844</v>
       </c>
       <c r="D49">
-        <v>1143.553840964466</v>
+        <v>1127.482696342716</v>
       </c>
       <c r="E49">
-        <v>1463.447</v>
+        <v>1496.448</v>
       </c>
       <c r="F49">
-        <v>1551.047</v>
+        <v>1584.048</v>
       </c>
       <c r="G49">
         <v>233.8</v>
@@ -5305,37 +5305,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M49">
-        <v>365.7368826</v>
+        <v>373.5185184</v>
       </c>
       <c r="N49">
-        <v>-273.6368826</v>
+        <v>-281.4185184</v>
       </c>
       <c r="O49">
-        <v>-49.25463886800001</v>
+        <v>-50.655333312</v>
       </c>
       <c r="P49">
-        <v>-224.382243732</v>
+        <v>-230.763185088</v>
       </c>
       <c r="Q49">
-        <v>77.21775626799999</v>
+        <v>70.83681491199999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1041444871238797</v>
+        <v>0.1052664964916466</v>
       </c>
       <c r="T49">
-        <v>0.9837718718595728</v>
+        <v>1.002690561703026</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.04532766802775826</v>
+        <v>0.04438334161051329</v>
       </c>
       <c r="W49">
-        <v>0.2251117358790546</v>
+        <v>0.225334408048241</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2518203779319903</v>
+        <v>0.2465741200584072</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1628990940388119</v>
+        <v>0.1647990940388119</v>
       </c>
       <c r="C50">
-        <v>-222.7653036572844</v>
+        <v>-271.3919910102388</v>
       </c>
       <c r="D50">
-        <v>1127.482696342716</v>
+        <v>1111.857008989761</v>
       </c>
       <c r="E50">
-        <v>1496.448</v>
+        <v>1529.449</v>
       </c>
       <c r="F50">
-        <v>1584.048</v>
+        <v>1617.049</v>
       </c>
       <c r="G50">
         <v>233.8</v>
@@ -5387,37 +5387,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M50">
-        <v>373.5185184</v>
+        <v>381.3001542</v>
       </c>
       <c r="N50">
-        <v>-281.4185184</v>
+        <v>-289.2001542</v>
       </c>
       <c r="O50">
-        <v>-50.655333312</v>
+        <v>-52.05602775600001</v>
       </c>
       <c r="P50">
-        <v>-230.763185088</v>
+        <v>-237.1441264440001</v>
       </c>
       <c r="Q50">
-        <v>70.83681491199999</v>
+        <v>64.45587355599997</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1052664964916466</v>
+        <v>0.1064325062267769</v>
       </c>
       <c r="T50">
-        <v>1.002690561703026</v>
+        <v>1.022351160952105</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.04438334161051329</v>
+        <v>0.04347755912866608</v>
       </c>
       <c r="W50">
-        <v>0.225334408048241</v>
+        <v>0.2255479915574606</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2465741200584072</v>
+        <v>0.241541995159256</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1647990940388119</v>
+        <v>0.1666990940388119</v>
       </c>
       <c r="C51">
-        <v>-271.3919910102388</v>
+        <v>-319.5914885905793</v>
       </c>
       <c r="D51">
-        <v>1111.857008989761</v>
+        <v>1096.658511409421</v>
       </c>
       <c r="E51">
-        <v>1529.449</v>
+        <v>1562.45</v>
       </c>
       <c r="F51">
-        <v>1617.049</v>
+        <v>1650.05</v>
       </c>
       <c r="G51">
         <v>233.8</v>
@@ -5469,37 +5469,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M51">
-        <v>381.3001542</v>
+        <v>389.08179</v>
       </c>
       <c r="N51">
-        <v>-289.2001542</v>
+        <v>-296.98179</v>
       </c>
       <c r="O51">
-        <v>-52.05602775600001</v>
+        <v>-53.45672220000001</v>
       </c>
       <c r="P51">
-        <v>-237.1441264440001</v>
+        <v>-243.5250678</v>
       </c>
       <c r="Q51">
-        <v>64.45587355599997</v>
+        <v>58.07493219999998</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1064325062267769</v>
+        <v>0.1076451563513125</v>
       </c>
       <c r="T51">
-        <v>1.022351160952105</v>
+        <v>1.042798184171147</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.04347755912866608</v>
+        <v>0.04260800794609276</v>
       </c>
       <c r="W51">
-        <v>0.2255479915574606</v>
+        <v>0.2257530317263113</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.241541995159256</v>
+        <v>0.2367111552560709</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1666990940388119</v>
+        <v>0.1685990940388119</v>
       </c>
       <c r="C52">
-        <v>-319.5914885905793</v>
+        <v>-367.381078535753</v>
       </c>
       <c r="D52">
-        <v>1096.658511409421</v>
+        <v>1081.869921464247</v>
       </c>
       <c r="E52">
-        <v>1562.45</v>
+        <v>1595.451</v>
       </c>
       <c r="F52">
-        <v>1650.05</v>
+        <v>1683.051</v>
       </c>
       <c r="G52">
         <v>233.8</v>
@@ -5551,37 +5551,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M52">
-        <v>389.08179</v>
+        <v>396.8634258</v>
       </c>
       <c r="N52">
-        <v>-296.98179</v>
+        <v>-304.7634258000001</v>
       </c>
       <c r="O52">
-        <v>-53.45672220000001</v>
+        <v>-54.857416644</v>
       </c>
       <c r="P52">
-        <v>-243.5250678</v>
+        <v>-249.906009156</v>
       </c>
       <c r="Q52">
-        <v>58.07493219999998</v>
+        <v>51.69399084399998</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1076451563513125</v>
+        <v>0.1089073023992984</v>
       </c>
       <c r="T52">
-        <v>1.042798184171147</v>
+        <v>1.064079779766477</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.04260800794609276</v>
+        <v>0.04177255680989485</v>
       </c>
       <c r="W52">
-        <v>0.2257530317263113</v>
+        <v>0.2259500311042268</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2367111552560709</v>
+        <v>0.2320697600549715</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1685990940388119</v>
+        <v>0.1704990940388119</v>
       </c>
       <c r="C53">
-        <v>-367.381078535753</v>
+        <v>-414.7771231789511</v>
       </c>
       <c r="D53">
-        <v>1081.869921464247</v>
+        <v>1067.474876821049</v>
       </c>
       <c r="E53">
-        <v>1595.451</v>
+        <v>1628.452</v>
       </c>
       <c r="F53">
-        <v>1683.051</v>
+        <v>1716.052</v>
       </c>
       <c r="G53">
         <v>233.8</v>
@@ -5633,37 +5633,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M53">
-        <v>396.8634258</v>
+        <v>404.6450616</v>
       </c>
       <c r="N53">
-        <v>-304.7634258000001</v>
+        <v>-312.5450616000001</v>
       </c>
       <c r="O53">
-        <v>-54.857416644</v>
+        <v>-56.25811108800001</v>
       </c>
       <c r="P53">
-        <v>-249.906009156</v>
+        <v>-256.286950512</v>
       </c>
       <c r="Q53">
-        <v>51.69399084399998</v>
+        <v>45.31304948799999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1089073023992984</v>
+        <v>0.1102220378659505</v>
       </c>
       <c r="T53">
-        <v>1.064079779766477</v>
+        <v>1.086248108511612</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.04177255680989485</v>
+        <v>0.04096923840970457</v>
       </c>
       <c r="W53">
-        <v>0.2259500311042268</v>
+        <v>0.2261394535829917</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2320697600549715</v>
+        <v>0.2276068800539143</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1704990940388119</v>
+        <v>0.1723990940388119</v>
       </c>
       <c r="C54">
-        <v>-414.7771231789511</v>
+        <v>-461.7951254388092</v>
       </c>
       <c r="D54">
-        <v>1067.474876821049</v>
+        <v>1053.457874561191</v>
       </c>
       <c r="E54">
-        <v>1628.452</v>
+        <v>1661.453</v>
       </c>
       <c r="F54">
-        <v>1716.052</v>
+        <v>1749.053</v>
       </c>
       <c r="G54">
         <v>233.8</v>
@@ -5715,37 +5715,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M54">
-        <v>404.6450616</v>
+        <v>412.4266974</v>
       </c>
       <c r="N54">
-        <v>-312.5450616000001</v>
+        <v>-320.3266974000001</v>
       </c>
       <c r="O54">
-        <v>-56.25811108800001</v>
+        <v>-57.65880553200001</v>
       </c>
       <c r="P54">
-        <v>-256.286950512</v>
+        <v>-262.667891868</v>
       </c>
       <c r="Q54">
-        <v>45.31304948799999</v>
+        <v>38.932108132</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1102220378659505</v>
+        <v>0.1115927195226728</v>
       </c>
       <c r="T54">
-        <v>1.086248108511612</v>
+        <v>1.109359770394838</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.04096923840970457</v>
+        <v>0.04019623391140826</v>
       </c>
       <c r="W54">
-        <v>0.2261394535829917</v>
+        <v>0.2263217280436899</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2276068800539143</v>
+        <v>0.2233124106189348</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1723990940388119</v>
+        <v>0.1742990940388119</v>
       </c>
       <c r="C55">
-        <v>-461.7951254388092</v>
+        <v>-508.4497845129195</v>
       </c>
       <c r="D55">
-        <v>1053.457874561191</v>
+        <v>1039.804215487081</v>
       </c>
       <c r="E55">
-        <v>1661.453</v>
+        <v>1694.454</v>
       </c>
       <c r="F55">
-        <v>1749.053</v>
+        <v>1782.054</v>
       </c>
       <c r="G55">
         <v>233.8</v>
@@ -5797,37 +5797,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M55">
-        <v>412.4266974</v>
+        <v>420.2083332</v>
       </c>
       <c r="N55">
-        <v>-320.3266974000001</v>
+        <v>-328.1083332000001</v>
       </c>
       <c r="O55">
-        <v>-57.65880553200001</v>
+        <v>-59.05949997600001</v>
       </c>
       <c r="P55">
-        <v>-262.667891868</v>
+        <v>-269.0488332240001</v>
       </c>
       <c r="Q55">
-        <v>38.932108132</v>
+        <v>32.55116677599995</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1115927195226728</v>
+        <v>0.1130229960340353</v>
       </c>
       <c r="T55">
-        <v>1.109359770394838</v>
+        <v>1.133476287142551</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.04019623391140826</v>
+        <v>0.03945185920934514</v>
       </c>
       <c r="W55">
-        <v>0.2263217280436899</v>
+        <v>0.2264972515984364</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2233124106189348</v>
+        <v>0.2191769956074731</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1742990940388119</v>
+        <v>0.1761990940388119</v>
       </c>
       <c r="C56">
-        <v>-508.4497845129195</v>
+        <v>-554.7550472957591</v>
       </c>
       <c r="D56">
-        <v>1039.804215487081</v>
+        <v>1026.499952704241</v>
       </c>
       <c r="E56">
-        <v>1694.454</v>
+        <v>1727.455</v>
       </c>
       <c r="F56">
-        <v>1782.054</v>
+        <v>1815.055</v>
       </c>
       <c r="G56">
         <v>233.8</v>
@@ -5879,37 +5879,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M56">
-        <v>420.2083332</v>
+        <v>427.989969</v>
       </c>
       <c r="N56">
-        <v>-328.1083332000001</v>
+        <v>-335.8899690000001</v>
       </c>
       <c r="O56">
-        <v>-59.05949997600001</v>
+        <v>-60.46019442000001</v>
       </c>
       <c r="P56">
-        <v>-269.0488332240001</v>
+        <v>-275.4297745800001</v>
       </c>
       <c r="Q56">
-        <v>32.55116677599995</v>
+        <v>26.17022541999995</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1130229960340353</v>
+        <v>0.1145168403903472</v>
       </c>
       <c r="T56">
-        <v>1.133476287142551</v>
+        <v>1.158664649079053</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.03945185920934514</v>
+        <v>0.03873455267826614</v>
       </c>
       <c r="W56">
-        <v>0.2264972515984364</v>
+        <v>0.2266663924784649</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2191769956074731</v>
+        <v>0.2151919593237008</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1761990940388119</v>
+        <v>0.1780990940388119</v>
       </c>
       <c r="C57">
-        <v>-554.7550472957591</v>
+        <v>-600.7241558991436</v>
       </c>
       <c r="D57">
-        <v>1026.499952704241</v>
+        <v>1013.531844100856</v>
       </c>
       <c r="E57">
-        <v>1727.455</v>
+        <v>1760.456</v>
       </c>
       <c r="F57">
-        <v>1815.055</v>
+        <v>1848.056</v>
       </c>
       <c r="G57">
         <v>233.8</v>
@@ -5961,37 +5961,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M57">
-        <v>427.989969</v>
+        <v>435.7716048</v>
       </c>
       <c r="N57">
-        <v>-335.8899690000001</v>
+        <v>-343.6716048000001</v>
       </c>
       <c r="O57">
-        <v>-60.46019442000001</v>
+        <v>-61.86088886400001</v>
       </c>
       <c r="P57">
-        <v>-275.4297745800001</v>
+        <v>-281.8107159360001</v>
       </c>
       <c r="Q57">
-        <v>26.17022541999995</v>
+        <v>19.78928406399996</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1145168403903472</v>
+        <v>0.1160785867628551</v>
       </c>
       <c r="T57">
-        <v>1.158664649079053</v>
+        <v>1.184997936558122</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.03873455267826614</v>
+        <v>0.03804286423758282</v>
       </c>
       <c r="W57">
-        <v>0.2266663924784649</v>
+        <v>0.226829492612778</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2151919593237008</v>
+        <v>0.211349245764349</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1780990940388119</v>
+        <v>0.1799990940388119</v>
       </c>
       <c r="C58">
-        <v>-600.7241558991436</v>
+        <v>-646.3696916155707</v>
       </c>
       <c r="D58">
-        <v>1013.531844100856</v>
+        <v>1000.88730838443</v>
       </c>
       <c r="E58">
-        <v>1760.456</v>
+        <v>1793.457</v>
       </c>
       <c r="F58">
-        <v>1848.056</v>
+        <v>1881.057</v>
       </c>
       <c r="G58">
         <v>233.8</v>
@@ -6043,37 +6043,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M58">
-        <v>435.7716048</v>
+        <v>443.5532406000001</v>
       </c>
       <c r="N58">
-        <v>-343.6716048000001</v>
+        <v>-351.4532406000001</v>
       </c>
       <c r="O58">
-        <v>-61.86088886400001</v>
+        <v>-63.26158330800002</v>
       </c>
       <c r="P58">
-        <v>-281.8107159360001</v>
+        <v>-288.1916572920001</v>
       </c>
       <c r="Q58">
-        <v>19.78928406399996</v>
+        <v>13.40834270799991</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1160785867628551</v>
+        <v>0.1177129725015261</v>
       </c>
       <c r="T58">
-        <v>1.184997936558122</v>
+        <v>1.212556028105986</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.03804286423758282</v>
+        <v>0.03737544556674802</v>
       </c>
       <c r="W58">
-        <v>0.226829492612778</v>
+        <v>0.2269868699353608</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.211349245764349</v>
+        <v>0.2076413642597112</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1799990940388119</v>
+        <v>0.1818990940388119</v>
       </c>
       <c r="C59">
-        <v>-646.3696916155707</v>
+        <v>-691.7036156312629</v>
       </c>
       <c r="D59">
-        <v>1000.88730838443</v>
+        <v>988.5543843687373</v>
       </c>
       <c r="E59">
-        <v>1793.457</v>
+        <v>1826.458</v>
       </c>
       <c r="F59">
-        <v>1881.057</v>
+        <v>1914.058</v>
       </c>
       <c r="G59">
         <v>233.8</v>
@@ -6125,37 +6125,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M59">
-        <v>443.5532406000001</v>
+        <v>451.3348764000001</v>
       </c>
       <c r="N59">
-        <v>-351.4532406000001</v>
+        <v>-359.2348764000001</v>
       </c>
       <c r="O59">
-        <v>-63.26158330800002</v>
+        <v>-64.66227775200002</v>
       </c>
       <c r="P59">
-        <v>-288.1916572920001</v>
+        <v>-294.5725986480001</v>
       </c>
       <c r="Q59">
-        <v>13.40834270799991</v>
+        <v>7.027401351999913</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1177129725015261</v>
+        <v>0.1194251861325148</v>
       </c>
       <c r="T59">
-        <v>1.212556028105986</v>
+        <v>1.241426409727556</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03737544556674802</v>
+        <v>0.03673104133283858</v>
       </c>
       <c r="W59">
-        <v>0.2269868699353608</v>
+        <v>0.2271388204537167</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2076413642597112</v>
+        <v>0.2040613407379921</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1818990940388119</v>
+        <v>0.1837990940388119</v>
       </c>
       <c r="C60">
-        <v>-691.7036156312624</v>
+        <v>-736.7373067658637</v>
       </c>
       <c r="D60">
-        <v>988.5543843687373</v>
+        <v>976.5216932341361</v>
       </c>
       <c r="E60">
-        <v>1826.458</v>
+        <v>1859.459</v>
       </c>
       <c r="F60">
-        <v>1914.058</v>
+        <v>1947.059</v>
       </c>
       <c r="G60">
         <v>233.8</v>
@@ -6207,37 +6207,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M60">
-        <v>451.3348764</v>
+        <v>459.1165121999999</v>
       </c>
       <c r="N60">
-        <v>-359.2348764</v>
+        <v>-367.0165122</v>
       </c>
       <c r="O60">
-        <v>-64.66227775199999</v>
+        <v>-66.06297219599999</v>
       </c>
       <c r="P60">
-        <v>-294.5725986480001</v>
+        <v>-300.953540004</v>
       </c>
       <c r="Q60">
-        <v>7.02740135199997</v>
+        <v>0.6464599960000328</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1194251861325148</v>
+        <v>0.1212209223796493</v>
       </c>
       <c r="T60">
-        <v>1.241426409727556</v>
+        <v>1.27170510264774</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.03673104133283858</v>
+        <v>0.0361084813102481</v>
       </c>
       <c r="W60">
-        <v>0.2271388204537167</v>
+        <v>0.2272856201070435</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2040613407379921</v>
+        <v>0.2006026739458228</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1837990940388119</v>
+        <v>0.1856990940388119</v>
       </c>
       <c r="C61">
-        <v>-736.7373067658637</v>
+        <v>-781.4815964890622</v>
       </c>
       <c r="D61">
-        <v>976.5216932341361</v>
+        <v>964.7784035109378</v>
       </c>
       <c r="E61">
-        <v>1859.459</v>
+        <v>1892.46</v>
       </c>
       <c r="F61">
-        <v>1947.059</v>
+        <v>1980.06</v>
       </c>
       <c r="G61">
         <v>233.8</v>
@@ -6289,37 +6289,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M61">
-        <v>459.1165121999999</v>
+        <v>466.898148</v>
       </c>
       <c r="N61">
-        <v>-367.0165122</v>
+        <v>-374.798148</v>
       </c>
       <c r="O61">
-        <v>-66.06297219599999</v>
+        <v>-67.46366664</v>
       </c>
       <c r="P61">
-        <v>-300.953540004</v>
+        <v>-307.33448136</v>
       </c>
       <c r="Q61">
-        <v>0.6464599960000328</v>
+        <v>-5.734481360000018</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1212209223796493</v>
+        <v>0.1231064454391406</v>
       </c>
       <c r="T61">
-        <v>1.27170510264774</v>
+        <v>1.303497730213934</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.0361084813102481</v>
+        <v>0.03550667328841063</v>
       </c>
       <c r="W61">
-        <v>0.2272856201070435</v>
+        <v>0.2274275264385928</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2006026739458228</v>
+        <v>0.1972592960467258</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1856990940388119</v>
+        <v>0.1875990940388119</v>
       </c>
       <c r="C62">
-        <v>-781.4815964890622</v>
+        <v>-825.9468014406641</v>
       </c>
       <c r="D62">
-        <v>964.7784035109378</v>
+        <v>953.3141985593358</v>
       </c>
       <c r="E62">
-        <v>1892.46</v>
+        <v>1925.461</v>
       </c>
       <c r="F62">
-        <v>1980.06</v>
+        <v>2013.061</v>
       </c>
       <c r="G62">
         <v>233.8</v>
@@ -6371,37 +6371,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M62">
-        <v>466.898148</v>
+        <v>474.6797838</v>
       </c>
       <c r="N62">
-        <v>-374.798148</v>
+        <v>-382.5797838</v>
       </c>
       <c r="O62">
-        <v>-67.46366664</v>
+        <v>-68.86436108400001</v>
       </c>
       <c r="P62">
-        <v>-307.33448136</v>
+        <v>-313.715422716</v>
       </c>
       <c r="Q62">
-        <v>-5.734481360000018</v>
+        <v>-12.11542271600001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1231064454391406</v>
+        <v>0.1250886619888621</v>
       </c>
       <c r="T62">
-        <v>1.303497730213934</v>
+        <v>1.336920748937368</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03550667328841063</v>
+        <v>0.03492459667712521</v>
       </c>
       <c r="W62">
-        <v>0.2274275264385928</v>
+        <v>0.2275647801035339</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1972592960467258</v>
+        <v>0.19402553709514</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1875990940388119</v>
+        <v>0.1894990940388119</v>
       </c>
       <c r="C63">
-        <v>-825.9468014406641</v>
+        <v>-870.1427536593224</v>
       </c>
       <c r="D63">
-        <v>953.3141985593358</v>
+        <v>942.1192463406776</v>
       </c>
       <c r="E63">
-        <v>1925.461</v>
+        <v>1958.462</v>
       </c>
       <c r="F63">
-        <v>2013.061</v>
+        <v>2046.062</v>
       </c>
       <c r="G63">
         <v>233.8</v>
@@ -6453,37 +6453,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M63">
-        <v>474.6797838</v>
+        <v>482.4614196</v>
       </c>
       <c r="N63">
-        <v>-382.5797838</v>
+        <v>-390.3614196</v>
       </c>
       <c r="O63">
-        <v>-68.86436108400001</v>
+        <v>-70.265055528</v>
       </c>
       <c r="P63">
-        <v>-313.715422716</v>
+        <v>-320.096364072</v>
       </c>
       <c r="Q63">
-        <v>-12.11542271600001</v>
+        <v>-18.49636407200001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1250886619888621</v>
+        <v>0.1271752057254111</v>
       </c>
       <c r="T63">
-        <v>1.336920748937368</v>
+        <v>1.372102873909404</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.03492459667712521</v>
+        <v>0.03436129673071996</v>
       </c>
       <c r="W63">
-        <v>0.2275647801035339</v>
+        <v>0.2276976062308962</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.19402553709514</v>
+        <v>0.1908960929484442</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1894990940388119</v>
+        <v>0.1913990940388119</v>
       </c>
       <c r="C64">
-        <v>-870.1427536593224</v>
+        <v>-914.0788287061011</v>
       </c>
       <c r="D64">
-        <v>942.1192463406776</v>
+        <v>931.1841712938989</v>
       </c>
       <c r="E64">
-        <v>1958.462</v>
+        <v>1991.463</v>
       </c>
       <c r="F64">
-        <v>2046.062</v>
+        <v>2079.063</v>
       </c>
       <c r="G64">
         <v>233.8</v>
@@ -6535,37 +6535,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M64">
-        <v>482.4614196</v>
+        <v>490.2430554000001</v>
       </c>
       <c r="N64">
-        <v>-390.3614196</v>
+        <v>-398.1430554000001</v>
       </c>
       <c r="O64">
-        <v>-70.265055528</v>
+        <v>-71.66574997200001</v>
       </c>
       <c r="P64">
-        <v>-320.096364072</v>
+        <v>-326.4773054280001</v>
       </c>
       <c r="Q64">
-        <v>-18.49636407200001</v>
+        <v>-24.87730542800006</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1271752057254111</v>
+        <v>0.1293745356098817</v>
       </c>
       <c r="T64">
-        <v>1.372102873909404</v>
+        <v>1.409186735366415</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.03436129673071996</v>
+        <v>0.03381587932229584</v>
       </c>
       <c r="W64">
-        <v>0.2276976062308962</v>
+        <v>0.2278262156558027</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1908960929484442</v>
+        <v>0.1878659962349769</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1913990940388119</v>
+        <v>0.1932990940388119</v>
       </c>
       <c r="C65">
-        <v>-914.0788287061011</v>
+        <v>-957.7639718519472</v>
       </c>
       <c r="D65">
-        <v>931.1841712938989</v>
+        <v>920.5000281480526</v>
       </c>
       <c r="E65">
-        <v>1991.463</v>
+        <v>2024.464</v>
       </c>
       <c r="F65">
-        <v>2079.063</v>
+        <v>2112.064</v>
       </c>
       <c r="G65">
         <v>233.8</v>
@@ -6617,37 +6617,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M65">
-        <v>490.2430554000001</v>
+        <v>498.0246912</v>
       </c>
       <c r="N65">
-        <v>-398.1430554000001</v>
+        <v>-405.9246912</v>
       </c>
       <c r="O65">
-        <v>-71.66574997200001</v>
+        <v>-73.06644441600001</v>
       </c>
       <c r="P65">
-        <v>-326.4773054280001</v>
+        <v>-332.858246784</v>
       </c>
       <c r="Q65">
-        <v>-24.87730542800006</v>
+        <v>-31.25824678399999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1293745356098817</v>
+        <v>0.131696050487934</v>
       </c>
       <c r="T65">
-        <v>1.409186735366415</v>
+        <v>1.448330811348816</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03381587932229584</v>
+        <v>0.03328750620788497</v>
       </c>
       <c r="W65">
-        <v>0.2278262156558027</v>
+        <v>0.2279508060361807</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1878659962349769</v>
+        <v>0.1849305900438054</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1932990940388119</v>
+        <v>0.1951990940388119</v>
       </c>
       <c r="C66">
-        <v>-957.7639718519472</v>
+        <v>-1001.206722482809</v>
       </c>
       <c r="D66">
-        <v>920.5000281480526</v>
+        <v>910.0582775171915</v>
       </c>
       <c r="E66">
-        <v>2024.464</v>
+        <v>2057.465</v>
       </c>
       <c r="F66">
-        <v>2112.064</v>
+        <v>2145.065</v>
       </c>
       <c r="G66">
         <v>233.8</v>
@@ -6699,37 +6699,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M66">
-        <v>498.0246912</v>
+        <v>505.806327</v>
       </c>
       <c r="N66">
-        <v>-405.9246912</v>
+        <v>-413.706327</v>
       </c>
       <c r="O66">
-        <v>-73.06644441600001</v>
+        <v>-74.46713886000001</v>
       </c>
       <c r="P66">
-        <v>-332.858246784</v>
+        <v>-339.23918814</v>
       </c>
       <c r="Q66">
-        <v>-31.25824678399999</v>
+        <v>-37.63918813999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.131696050487934</v>
+        <v>0.1341502233590178</v>
       </c>
       <c r="T66">
-        <v>1.448330811348816</v>
+        <v>1.489711691673068</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03328750620788497</v>
+        <v>0.03277539072776366</v>
       </c>
       <c r="W66">
-        <v>0.2279508060361807</v>
+        <v>0.2280715628663933</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1849305900438054</v>
+        <v>0.1820855040431314</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1951990940388119</v>
+        <v>0.1970990940388119</v>
       </c>
       <c r="C67">
-        <v>-1001.206722482809</v>
+        <v>-1044.415236862333</v>
       </c>
       <c r="D67">
-        <v>910.0582775171915</v>
+        <v>899.8507631376672</v>
       </c>
       <c r="E67">
-        <v>2057.465</v>
+        <v>2090.466</v>
       </c>
       <c r="F67">
-        <v>2145.065</v>
+        <v>2178.066</v>
       </c>
       <c r="G67">
         <v>233.8</v>
@@ -6781,37 +6781,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M67">
-        <v>505.806327</v>
+        <v>513.5879628000001</v>
       </c>
       <c r="N67">
-        <v>-413.706327</v>
+        <v>-421.4879628000002</v>
       </c>
       <c r="O67">
-        <v>-74.46713886000001</v>
+        <v>-75.86783330400003</v>
       </c>
       <c r="P67">
-        <v>-339.23918814</v>
+        <v>-345.6201294960001</v>
       </c>
       <c r="Q67">
-        <v>-37.63918813999999</v>
+        <v>-44.0201294960001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1341502233590178</v>
+        <v>0.1367487593401654</v>
       </c>
       <c r="T67">
-        <v>1.489711691673068</v>
+        <v>1.533526741428158</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03277539072776366</v>
+        <v>0.03227879389855511</v>
       </c>
       <c r="W67">
-        <v>0.2280715628663933</v>
+        <v>0.2281886603987207</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1820855040431314</v>
+        <v>0.1793266327697506</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1970990940388119</v>
+        <v>0.1989990940388119</v>
       </c>
       <c r="C68">
-        <v>-1044.415236862333</v>
+        <v>-1087.397309379679</v>
       </c>
       <c r="D68">
-        <v>899.8507631376672</v>
+        <v>889.8696906203215</v>
       </c>
       <c r="E68">
-        <v>2090.466</v>
+        <v>2123.467</v>
       </c>
       <c r="F68">
-        <v>2178.066</v>
+        <v>2211.067</v>
       </c>
       <c r="G68">
         <v>233.8</v>
@@ -6863,37 +6863,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M68">
-        <v>513.5879628000001</v>
+        <v>521.3695986</v>
       </c>
       <c r="N68">
-        <v>-421.4879628000002</v>
+        <v>-429.2695986000001</v>
       </c>
       <c r="O68">
-        <v>-75.86783330400003</v>
+        <v>-77.26852774800001</v>
       </c>
       <c r="P68">
-        <v>-345.6201294960001</v>
+        <v>-352.0010708520001</v>
       </c>
       <c r="Q68">
-        <v>-44.0201294960001</v>
+        <v>-50.40107085200003</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1367487593401654</v>
+        <v>0.1395047823504734</v>
       </c>
       <c r="T68">
-        <v>1.533526741428158</v>
+        <v>1.579997248744163</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03227879389855511</v>
+        <v>0.0317970208552931</v>
       </c>
       <c r="W68">
-        <v>0.2281886603987207</v>
+        <v>0.2283022624823219</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1793266327697506</v>
+        <v>0.1766501158627395</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1989990940388119</v>
+        <v>0.2008990940388119</v>
       </c>
       <c r="C69">
-        <v>-1087.397309379679</v>
+        <v>-1130.160392398762</v>
       </c>
       <c r="D69">
-        <v>889.8696906203215</v>
+        <v>880.1076076012382</v>
       </c>
       <c r="E69">
-        <v>2123.467</v>
+        <v>2156.468</v>
       </c>
       <c r="F69">
-        <v>2211.067</v>
+        <v>2244.068</v>
       </c>
       <c r="G69">
         <v>233.8</v>
@@ -6945,37 +6945,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M69">
-        <v>521.3695986</v>
+        <v>529.1512344</v>
       </c>
       <c r="N69">
-        <v>-429.2695986000001</v>
+        <v>-437.0512344000001</v>
       </c>
       <c r="O69">
-        <v>-77.26852774800001</v>
+        <v>-78.66922219200001</v>
       </c>
       <c r="P69">
-        <v>-352.0010708520001</v>
+        <v>-358.382012208</v>
       </c>
       <c r="Q69">
-        <v>-50.40107085200003</v>
+        <v>-56.78201220800003</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1395047823504734</v>
+        <v>0.1424330567989257</v>
       </c>
       <c r="T69">
-        <v>1.579997248744163</v>
+        <v>1.629372162767418</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.0317970208552931</v>
+        <v>0.03132941760742115</v>
       </c>
       <c r="W69">
-        <v>0.2283022624823219</v>
+        <v>0.2284125233281701</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1766501158627395</v>
+        <v>0.1740523200412286</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2008990940388119</v>
+        <v>0.2027990940388119</v>
       </c>
       <c r="C70">
-        <v>-1130.160392398762</v>
+        <v>-1172.711614815177</v>
       </c>
       <c r="D70">
-        <v>880.1076076012382</v>
+        <v>870.5573851848231</v>
       </c>
       <c r="E70">
-        <v>2156.468</v>
+        <v>2189.469</v>
       </c>
       <c r="F70">
-        <v>2244.068</v>
+        <v>2277.069</v>
       </c>
       <c r="G70">
         <v>233.8</v>
@@ -7027,37 +7027,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M70">
-        <v>529.1512344</v>
+        <v>536.9328702</v>
       </c>
       <c r="N70">
-        <v>-437.0512344000001</v>
+        <v>-444.8328702000001</v>
       </c>
       <c r="O70">
-        <v>-78.66922219200001</v>
+        <v>-80.069916636</v>
       </c>
       <c r="P70">
-        <v>-358.382012208</v>
+        <v>-364.762953564</v>
       </c>
       <c r="Q70">
-        <v>-56.78201220800003</v>
+        <v>-63.16295356400002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1424330567989257</v>
+        <v>0.1455502521795362</v>
       </c>
       <c r="T70">
-        <v>1.629372162767418</v>
+        <v>1.681932555114754</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03132941760742115</v>
+        <v>0.03087536807687881</v>
       </c>
       <c r="W70">
-        <v>0.2284125233281701</v>
+        <v>0.228519588207472</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1740523200412286</v>
+        <v>0.1715298226493267</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2027990940388119</v>
+        <v>0.2046990940388119</v>
       </c>
       <c r="C71">
-        <v>-1172.711614815177</v>
+        <v>-1215.057799417894</v>
       </c>
       <c r="D71">
-        <v>870.5573851848231</v>
+        <v>861.212200582106</v>
       </c>
       <c r="E71">
-        <v>2189.469</v>
+        <v>2222.47</v>
       </c>
       <c r="F71">
-        <v>2277.069</v>
+        <v>2310.07</v>
       </c>
       <c r="G71">
         <v>233.8</v>
@@ -7109,37 +7109,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M71">
-        <v>536.9328702</v>
+        <v>544.714506</v>
       </c>
       <c r="N71">
-        <v>-444.8328702000001</v>
+        <v>-452.6145060000001</v>
       </c>
       <c r="O71">
-        <v>-80.069916636</v>
+        <v>-81.47061108000001</v>
       </c>
       <c r="P71">
-        <v>-364.762953564</v>
+        <v>-371.14389492</v>
       </c>
       <c r="Q71">
-        <v>-63.16295356400002</v>
+        <v>-69.54389492000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1455502521795362</v>
+        <v>0.1488752605855208</v>
       </c>
       <c r="T71">
-        <v>1.681932555114754</v>
+        <v>1.737996973618579</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03087536807687881</v>
+        <v>0.03043429139006625</v>
       </c>
       <c r="W71">
-        <v>0.228519588207472</v>
+        <v>0.2286235940902224</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1715298226493267</v>
+        <v>0.1690793966114792</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2046990940388119</v>
+        <v>0.2065990940388119</v>
       </c>
       <c r="C72">
-        <v>-1215.057799417894</v>
+        <v>-1257.2054791446</v>
       </c>
       <c r="D72">
-        <v>861.212200582106</v>
+        <v>852.0655208554001</v>
       </c>
       <c r="E72">
-        <v>2222.47</v>
+        <v>2255.471</v>
       </c>
       <c r="F72">
-        <v>2310.07</v>
+        <v>2343.071</v>
       </c>
       <c r="G72">
         <v>233.8</v>
@@ -7191,37 +7191,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M72">
-        <v>544.714506</v>
+        <v>552.4961418000001</v>
       </c>
       <c r="N72">
-        <v>-452.6145060000001</v>
+        <v>-460.3961418000002</v>
       </c>
       <c r="O72">
-        <v>-81.47061108000001</v>
+        <v>-82.87130552400004</v>
       </c>
       <c r="P72">
-        <v>-371.14389492</v>
+        <v>-377.5248362760001</v>
       </c>
       <c r="Q72">
-        <v>-69.54389492000001</v>
+        <v>-75.92483627600012</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1488752605855208</v>
+        <v>0.152429579916056</v>
       </c>
       <c r="T72">
-        <v>1.737996973618579</v>
+        <v>1.797927903743358</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03043429139006625</v>
+        <v>0.03000563939865686</v>
       </c>
       <c r="W72">
-        <v>0.2286235940902224</v>
+        <v>0.2287246702297967</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1690793966114792</v>
+        <v>0.1666979966592048</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2065990940388119</v>
+        <v>0.2084990940388119</v>
       </c>
       <c r="C73">
-        <v>-1257.2054791446</v>
+        <v>-1299.160912312062</v>
       </c>
       <c r="D73">
-        <v>852.0655208553998</v>
+        <v>843.1110876879375</v>
       </c>
       <c r="E73">
-        <v>2255.471</v>
+        <v>2288.472</v>
       </c>
       <c r="F73">
-        <v>2343.071</v>
+        <v>2376.072</v>
       </c>
       <c r="G73">
         <v>233.8</v>
@@ -7273,37 +7273,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M73">
-        <v>552.4961418</v>
+        <v>560.2777775999999</v>
       </c>
       <c r="N73">
-        <v>-460.3961418000001</v>
+        <v>-468.1777776</v>
       </c>
       <c r="O73">
-        <v>-82.87130552400001</v>
+        <v>-84.27199996799999</v>
       </c>
       <c r="P73">
-        <v>-377.5248362760001</v>
+        <v>-383.905777632</v>
       </c>
       <c r="Q73">
-        <v>-75.92483627600006</v>
+        <v>-82.30577763199994</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.152429579916056</v>
+        <v>0.1562377791987722</v>
       </c>
       <c r="T73">
-        <v>1.797927903743357</v>
+        <v>1.862139614591334</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03000563939865687</v>
+        <v>0.02958889440700886</v>
       </c>
       <c r="W73">
-        <v>0.2287246702297967</v>
+        <v>0.2288229386988273</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1666979966592048</v>
+        <v>0.1643827467056048</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2084990940388119</v>
+        <v>0.2103990940388119</v>
       </c>
       <c r="C74">
-        <v>-1299.160912312062</v>
+        <v>-1340.930096896143</v>
       </c>
       <c r="D74">
-        <v>843.1110876879375</v>
+        <v>834.3429031038569</v>
       </c>
       <c r="E74">
-        <v>2288.472</v>
+        <v>2321.473</v>
       </c>
       <c r="F74">
-        <v>2376.072</v>
+        <v>2409.073</v>
       </c>
       <c r="G74">
         <v>233.8</v>
@@ -7355,37 +7355,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M74">
-        <v>560.2777775999999</v>
+        <v>568.0594134</v>
       </c>
       <c r="N74">
-        <v>-468.1777776</v>
+        <v>-475.9594134000001</v>
       </c>
       <c r="O74">
-        <v>-84.27199996799999</v>
+        <v>-85.67269441200001</v>
       </c>
       <c r="P74">
-        <v>-383.905777632</v>
+        <v>-390.2867189880001</v>
       </c>
       <c r="Q74">
-        <v>-82.30577763199994</v>
+        <v>-88.68671898800005</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1562377791987722</v>
+        <v>0.1603280673172453</v>
       </c>
       <c r="T74">
-        <v>1.862139614591334</v>
+        <v>1.931107748465087</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02958889440700886</v>
+        <v>0.0291835670863649</v>
       </c>
       <c r="W74">
-        <v>0.2288229386988273</v>
+        <v>0.2289185148810352</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1643827467056048</v>
+        <v>0.1621309282575828</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2103990940388119</v>
+        <v>0.2122990940388119</v>
       </c>
       <c r="C75">
-        <v>-1340.930096896143</v>
+        <v>-1382.518783929917</v>
       </c>
       <c r="D75">
-        <v>834.3429031038569</v>
+        <v>825.7552160700826</v>
       </c>
       <c r="E75">
-        <v>2321.473</v>
+        <v>2354.474</v>
       </c>
       <c r="F75">
-        <v>2409.073</v>
+        <v>2442.074</v>
       </c>
       <c r="G75">
         <v>233.8</v>
@@ -7437,37 +7437,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M75">
-        <v>568.0594134</v>
+        <v>575.8410492</v>
       </c>
       <c r="N75">
-        <v>-475.9594134000001</v>
+        <v>-483.7410492000001</v>
       </c>
       <c r="O75">
-        <v>-85.67269441200001</v>
+        <v>-87.07338885600001</v>
       </c>
       <c r="P75">
-        <v>-390.2867189880001</v>
+        <v>-396.6676603440001</v>
       </c>
       <c r="Q75">
-        <v>-88.68671898800005</v>
+        <v>-95.06766034400005</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1603280673172453</v>
+        <v>0.1647329929832932</v>
       </c>
       <c r="T75">
-        <v>1.931107748465087</v>
+        <v>2.005381123406052</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.0291835670863649</v>
+        <v>0.02878919455817078</v>
       </c>
       <c r="W75">
-        <v>0.2289185148810352</v>
+        <v>0.2290115079231833</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1621309282575828</v>
+        <v>0.1599399697676155</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2122990940388119</v>
+        <v>0.2141990940388119</v>
       </c>
       <c r="C76">
-        <v>-1382.518783929917</v>
+        <v>-1423.932490082816</v>
       </c>
       <c r="D76">
-        <v>825.7552160700826</v>
+        <v>817.3425099171842</v>
       </c>
       <c r="E76">
-        <v>2354.474</v>
+        <v>2387.475</v>
       </c>
       <c r="F76">
-        <v>2442.074</v>
+        <v>2475.075</v>
       </c>
       <c r="G76">
         <v>233.8</v>
@@ -7519,37 +7519,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M76">
-        <v>575.8410492</v>
+        <v>583.6226849999999</v>
       </c>
       <c r="N76">
-        <v>-483.7410492000001</v>
+        <v>-491.522685</v>
       </c>
       <c r="O76">
-        <v>-87.07338885600001</v>
+        <v>-88.47408329999999</v>
       </c>
       <c r="P76">
-        <v>-396.6676603440001</v>
+        <v>-403.0486016999999</v>
       </c>
       <c r="Q76">
-        <v>-95.06766034400005</v>
+        <v>-101.4486016999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1647329929832932</v>
+        <v>0.1694903127026249</v>
       </c>
       <c r="T76">
-        <v>2.005381123406052</v>
+        <v>2.085596368342295</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02878919455817078</v>
+        <v>0.02840533863072851</v>
       </c>
       <c r="W76">
-        <v>0.2290115079231833</v>
+        <v>0.2291020211508742</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1599399697676155</v>
+        <v>0.1578074368373806</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2141990940388119</v>
+        <v>0.2160990940388119</v>
       </c>
       <c r="C77">
-        <v>-1423.932490082816</v>
+        <v>-1465.176509478577</v>
       </c>
       <c r="D77">
-        <v>817.3425099171842</v>
+        <v>809.0994905214234</v>
       </c>
       <c r="E77">
-        <v>2387.475</v>
+        <v>2420.476</v>
       </c>
       <c r="F77">
-        <v>2475.075</v>
+        <v>2508.076</v>
       </c>
       <c r="G77">
         <v>233.8</v>
@@ -7601,37 +7601,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M77">
-        <v>583.6226849999999</v>
+        <v>591.4043208000001</v>
       </c>
       <c r="N77">
-        <v>-491.522685</v>
+        <v>-499.3043208000001</v>
       </c>
       <c r="O77">
-        <v>-88.47408329999999</v>
+        <v>-89.87477774400001</v>
       </c>
       <c r="P77">
-        <v>-403.0486016999999</v>
+        <v>-409.4295430560001</v>
       </c>
       <c r="Q77">
-        <v>-101.4486016999999</v>
+        <v>-107.829543056</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1694903127026249</v>
+        <v>0.174644075731901</v>
       </c>
       <c r="T77">
-        <v>2.085596368342295</v>
+        <v>2.172496217023224</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02840533863072851</v>
+        <v>0.02803158417506102</v>
       </c>
       <c r="W77">
-        <v>0.2291020211508742</v>
+        <v>0.2291901524515206</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1578074368373806</v>
+        <v>0.1557310231947835</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2160990940388119</v>
+        <v>0.2179990940388119</v>
       </c>
       <c r="C78">
-        <v>-1465.176509478577</v>
+        <v>-1506.255924805233</v>
       </c>
       <c r="D78">
-        <v>809.0994905214234</v>
+        <v>801.0210751947664</v>
       </c>
       <c r="E78">
-        <v>2420.476</v>
+        <v>2453.477</v>
       </c>
       <c r="F78">
-        <v>2508.076</v>
+        <v>2541.077</v>
       </c>
       <c r="G78">
         <v>233.8</v>
@@ -7683,37 +7683,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M78">
-        <v>591.4043208000001</v>
+        <v>599.1859565999999</v>
       </c>
       <c r="N78">
-        <v>-499.3043208000001</v>
+        <v>-507.0859566</v>
       </c>
       <c r="O78">
-        <v>-89.87477774400001</v>
+        <v>-91.27547218799999</v>
       </c>
       <c r="P78">
-        <v>-409.4295430560001</v>
+        <v>-415.810484412</v>
       </c>
       <c r="Q78">
-        <v>-107.829543056</v>
+        <v>-114.210484412</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.174644075731901</v>
+        <v>0.1802459920680706</v>
       </c>
       <c r="T78">
-        <v>2.172496217023224</v>
+        <v>2.266952574285103</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02803158417506102</v>
+        <v>0.02766753762733296</v>
       </c>
       <c r="W78">
-        <v>0.2291901524515206</v>
+        <v>0.2292759946274749</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1557310231947835</v>
+        <v>0.1537085423740721</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2179990940388119</v>
+        <v>0.2198990940388119</v>
       </c>
       <c r="C79">
-        <v>-1506.255924805233</v>
+        <v>-1547.175617766118</v>
       </c>
       <c r="D79">
-        <v>801.0210751947664</v>
+        <v>793.1023822338821</v>
       </c>
       <c r="E79">
-        <v>2453.477</v>
+        <v>2486.478</v>
       </c>
       <c r="F79">
-        <v>2541.077</v>
+        <v>2574.078</v>
       </c>
       <c r="G79">
         <v>233.8</v>
@@ -7765,37 +7765,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M79">
-        <v>599.1859565999999</v>
+        <v>606.9675924000001</v>
       </c>
       <c r="N79">
-        <v>-507.0859566</v>
+        <v>-514.8675924000001</v>
       </c>
       <c r="O79">
-        <v>-91.27547218799999</v>
+        <v>-92.67616663200002</v>
       </c>
       <c r="P79">
-        <v>-415.810484412</v>
+        <v>-422.1914257680002</v>
       </c>
       <c r="Q79">
-        <v>-114.210484412</v>
+        <v>-120.5914257680001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1802459920680706</v>
+        <v>0.1863571735257101</v>
       </c>
       <c r="T79">
-        <v>2.266952574285103</v>
+        <v>2.369995873116244</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02766753762733296</v>
+        <v>0.02731282560646971</v>
       </c>
       <c r="W79">
-        <v>0.2292759946274749</v>
+        <v>0.2293596357219944</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1537085423740721</v>
+        <v>0.1517379200359428</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2198990940388119</v>
+        <v>0.2217990940388119</v>
       </c>
       <c r="C80">
-        <v>-1547.175617766118</v>
+        <v>-1587.940278917027</v>
       </c>
       <c r="D80">
-        <v>793.1023822338821</v>
+        <v>785.3387210829732</v>
       </c>
       <c r="E80">
-        <v>2486.478</v>
+        <v>2519.479</v>
       </c>
       <c r="F80">
-        <v>2574.078</v>
+        <v>2607.079</v>
       </c>
       <c r="G80">
         <v>233.8</v>
@@ -7847,37 +7847,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M80">
-        <v>606.9675924000001</v>
+        <v>614.7492282000001</v>
       </c>
       <c r="N80">
-        <v>-514.8675924000001</v>
+        <v>-522.6492282000002</v>
       </c>
       <c r="O80">
-        <v>-92.67616663200002</v>
+        <v>-94.07686107600003</v>
       </c>
       <c r="P80">
-        <v>-422.1914257680002</v>
+        <v>-428.5723671240002</v>
       </c>
       <c r="Q80">
-        <v>-120.5914257680001</v>
+        <v>-126.9723671240001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1863571735257101</v>
+        <v>0.1930503722650297</v>
       </c>
       <c r="T80">
-        <v>2.369995873116244</v>
+        <v>2.482852819455113</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02731282560646971</v>
+        <v>0.02696709363676757</v>
       </c>
       <c r="W80">
-        <v>0.2293596357219944</v>
+        <v>0.2294411593204502</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1517379200359428</v>
+        <v>0.1498171868709308</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2217990940388119</v>
+        <v>0.2236990940388119</v>
       </c>
       <c r="C81">
-        <v>-1587.940278917027</v>
+        <v>-1628.55441693123</v>
       </c>
       <c r="D81">
-        <v>785.3387210829732</v>
+        <v>777.7255830687702</v>
       </c>
       <c r="E81">
-        <v>2519.479</v>
+        <v>2552.48</v>
       </c>
       <c r="F81">
-        <v>2607.079</v>
+        <v>2640.08</v>
       </c>
       <c r="G81">
         <v>233.8</v>
@@ -7929,37 +7929,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M81">
-        <v>614.7492282000001</v>
+        <v>622.530864</v>
       </c>
       <c r="N81">
-        <v>-522.6492282000002</v>
+        <v>-530.4308639999999</v>
       </c>
       <c r="O81">
-        <v>-94.07686107600003</v>
+        <v>-95.47755551999998</v>
       </c>
       <c r="P81">
-        <v>-428.5723671240002</v>
+        <v>-434.9533084799999</v>
       </c>
       <c r="Q81">
-        <v>-126.9723671240001</v>
+        <v>-133.3533084799999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1930503722650297</v>
+        <v>0.2004128908782812</v>
       </c>
       <c r="T81">
-        <v>2.482852819455113</v>
+        <v>2.606995460427869</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02696709363676757</v>
+        <v>0.02663000496630798</v>
       </c>
       <c r="W81">
-        <v>0.2294411593204502</v>
+        <v>0.2295206448289446</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1498171868709308</v>
+        <v>0.1479444720350443</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2236990940388119</v>
+        <v>0.2255990940388119</v>
       </c>
       <c r="C82">
-        <v>-1628.55441693123</v>
+        <v>-1669.022367330741</v>
       </c>
       <c r="D82">
-        <v>777.7255830687702</v>
+        <v>770.2586326692596</v>
       </c>
       <c r="E82">
-        <v>2552.48</v>
+        <v>2585.481</v>
       </c>
       <c r="F82">
-        <v>2640.08</v>
+        <v>2673.081</v>
       </c>
       <c r="G82">
         <v>233.8</v>
@@ -8011,37 +8011,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M82">
-        <v>622.530864</v>
+        <v>630.3124998000001</v>
       </c>
       <c r="N82">
-        <v>-530.4308639999999</v>
+        <v>-538.2124998000002</v>
       </c>
       <c r="O82">
-        <v>-95.47755551999998</v>
+        <v>-96.87824996400002</v>
       </c>
       <c r="P82">
-        <v>-434.9533084799999</v>
+        <v>-441.3342498360001</v>
       </c>
       <c r="Q82">
-        <v>-133.3533084799999</v>
+        <v>-139.7342498360001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2004128908782812</v>
+        <v>0.2085504114508223</v>
       </c>
       <c r="T82">
-        <v>2.606995460427869</v>
+        <v>2.744205747818809</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02663000496630798</v>
+        <v>0.02630123947289676</v>
       </c>
       <c r="W82">
-        <v>0.2295206448289446</v>
+        <v>0.2295981677322909</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1479444720350443</v>
+        <v>0.1461179970716486</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2255990940388119</v>
+        <v>0.2274990940388119</v>
       </c>
       <c r="C83">
-        <v>-1669.022367330741</v>
+        <v>-1709.348300719411</v>
       </c>
       <c r="D83">
-        <v>770.2586326692596</v>
+        <v>762.9336992805891</v>
       </c>
       <c r="E83">
-        <v>2585.481</v>
+        <v>2618.482</v>
       </c>
       <c r="F83">
-        <v>2673.081</v>
+        <v>2706.082</v>
       </c>
       <c r="G83">
         <v>233.8</v>
@@ -8093,37 +8093,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M83">
-        <v>630.3124998000001</v>
+        <v>638.0941356000001</v>
       </c>
       <c r="N83">
-        <v>-538.2124998000002</v>
+        <v>-545.9941356000002</v>
       </c>
       <c r="O83">
-        <v>-96.87824996400002</v>
+        <v>-98.27894440800003</v>
       </c>
       <c r="P83">
-        <v>-441.3342498360001</v>
+        <v>-447.7151911920001</v>
       </c>
       <c r="Q83">
-        <v>-139.7342498360001</v>
+        <v>-146.1151911920001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2085504114508223</v>
+        <v>0.217592100975868</v>
       </c>
       <c r="T83">
-        <v>2.744205747818809</v>
+        <v>2.896661622697632</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02630123947289676</v>
+        <v>0.02598049265005655</v>
       </c>
       <c r="W83">
-        <v>0.2295981677322909</v>
+        <v>0.2296737998331167</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1461179970716486</v>
+        <v>0.1443360702780919</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2274990940388119</v>
+        <v>0.2293990940388119</v>
       </c>
       <c r="C84">
-        <v>-1709.348300719411</v>
+        <v>-1749.536230550675</v>
       </c>
       <c r="D84">
-        <v>762.9336992805891</v>
+        <v>755.7467694493251</v>
       </c>
       <c r="E84">
-        <v>2618.482</v>
+        <v>2651.483</v>
       </c>
       <c r="F84">
-        <v>2706.082</v>
+        <v>2739.083</v>
       </c>
       <c r="G84">
         <v>233.8</v>
@@ -8175,37 +8175,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M84">
-        <v>638.0941356000001</v>
+        <v>645.8757714000001</v>
       </c>
       <c r="N84">
-        <v>-545.9941356000002</v>
+        <v>-553.7757714000002</v>
       </c>
       <c r="O84">
-        <v>-98.27894440800003</v>
+        <v>-99.67963885200002</v>
       </c>
       <c r="P84">
-        <v>-447.7151911920001</v>
+        <v>-454.0961325480001</v>
       </c>
       <c r="Q84">
-        <v>-146.1151911920001</v>
+        <v>-152.4961325480001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.217592100975868</v>
+        <v>0.2276975186803309</v>
       </c>
       <c r="T84">
-        <v>2.896661622697632</v>
+        <v>3.067053482856317</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02598049265005655</v>
+        <v>0.02566747466632094</v>
       </c>
       <c r="W84">
-        <v>0.2296737998331167</v>
+        <v>0.2297476094736815</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1443360702780919</v>
+        <v>0.1425970814795606</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2293990940388119</v>
+        <v>0.2312990940388119</v>
       </c>
       <c r="C85">
-        <v>-1749.536230550675</v>
+        <v>-1789.590020460356</v>
       </c>
       <c r="D85">
-        <v>755.7467694493251</v>
+        <v>748.6939795396446</v>
       </c>
       <c r="E85">
-        <v>2651.483</v>
+        <v>2684.484</v>
       </c>
       <c r="F85">
-        <v>2739.083</v>
+        <v>2772.084</v>
       </c>
       <c r="G85">
         <v>233.8</v>
@@ -8257,37 +8257,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M85">
-        <v>645.8757714000001</v>
+        <v>653.6574072000001</v>
       </c>
       <c r="N85">
-        <v>-553.7757714000002</v>
+        <v>-561.5574072000002</v>
       </c>
       <c r="O85">
-        <v>-99.67963885200002</v>
+        <v>-101.080333296</v>
       </c>
       <c r="P85">
-        <v>-454.0961325480001</v>
+        <v>-460.4770739040001</v>
       </c>
       <c r="Q85">
-        <v>-152.4961325480001</v>
+        <v>-158.8770739040001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2276975186803309</v>
+        <v>0.2390661135978515</v>
       </c>
       <c r="T85">
-        <v>3.067053482856317</v>
+        <v>3.258744325534837</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02566747466632094</v>
+        <v>0.02536190949172188</v>
       </c>
       <c r="W85">
-        <v>0.2297476094736815</v>
+        <v>0.229819661741852</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1425970814795606</v>
+        <v>0.1408994971762325</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2312990940388119</v>
+        <v>0.2331990940388119</v>
       </c>
       <c r="C86">
-        <v>-1789.590020460354</v>
+        <v>-1829.513391192678</v>
       </c>
       <c r="D86">
-        <v>748.6939795396453</v>
+        <v>741.7716088073224</v>
       </c>
       <c r="E86">
-        <v>2684.484</v>
+        <v>2717.485</v>
       </c>
       <c r="F86">
-        <v>2772.084</v>
+        <v>2805.085</v>
       </c>
       <c r="G86">
         <v>233.8</v>
@@ -8339,37 +8339,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M86">
-        <v>653.6574072</v>
+        <v>661.4390430000001</v>
       </c>
       <c r="N86">
-        <v>-561.5574071999999</v>
+        <v>-569.3390430000002</v>
       </c>
       <c r="O86">
-        <v>-101.080333296</v>
+        <v>-102.48102774</v>
       </c>
       <c r="P86">
-        <v>-460.477073904</v>
+        <v>-466.8580152600001</v>
       </c>
       <c r="Q86">
-        <v>-158.8770739039999</v>
+        <v>-165.2580152600001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2390661135978514</v>
+        <v>0.2519505211710415</v>
       </c>
       <c r="T86">
-        <v>3.258744325534835</v>
+        <v>3.475993947237157</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02536190949172188</v>
+        <v>0.02506353408593692</v>
       </c>
       <c r="W86">
-        <v>0.229819661741852</v>
+        <v>0.2298900186625361</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1408994971762327</v>
+        <v>0.1392418560329828</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2331990940388119</v>
+        <v>0.2350990940388119</v>
       </c>
       <c r="C87">
-        <v>-1829.513391192678</v>
+        <v>-1869.309927145582</v>
       </c>
       <c r="D87">
-        <v>741.7716088073224</v>
+        <v>734.9760728544176</v>
       </c>
       <c r="E87">
-        <v>2717.485</v>
+        <v>2750.486</v>
       </c>
       <c r="F87">
-        <v>2805.085</v>
+        <v>2838.086</v>
       </c>
       <c r="G87">
         <v>233.8</v>
@@ -8421,37 +8421,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M87">
-        <v>661.4390430000001</v>
+        <v>669.2206788</v>
       </c>
       <c r="N87">
-        <v>-569.3390430000002</v>
+        <v>-577.1206788</v>
       </c>
       <c r="O87">
-        <v>-102.48102774</v>
+        <v>-103.881722184</v>
       </c>
       <c r="P87">
-        <v>-466.8580152600001</v>
+        <v>-473.238956616</v>
       </c>
       <c r="Q87">
-        <v>-165.2580152600001</v>
+        <v>-171.638956616</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2519505211710415</v>
+        <v>0.2666755583975445</v>
       </c>
       <c r="T87">
-        <v>3.475993947237157</v>
+        <v>3.724279229182669</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02506353408593692</v>
+        <v>0.02477209764307719</v>
       </c>
       <c r="W87">
-        <v>0.2298900186625361</v>
+        <v>0.2299587393757624</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1392418560329828</v>
+        <v>0.1376227646837622</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2350990940388119</v>
+        <v>0.2369990940388119</v>
       </c>
       <c r="C88">
-        <v>-1869.309927145582</v>
+        <v>-1908.983082559519</v>
       </c>
       <c r="D88">
-        <v>734.9760728544176</v>
+        <v>728.3039174404809</v>
       </c>
       <c r="E88">
-        <v>2750.486</v>
+        <v>2783.487</v>
       </c>
       <c r="F88">
-        <v>2838.086</v>
+        <v>2871.087</v>
       </c>
       <c r="G88">
         <v>233.8</v>
@@ -8503,37 +8503,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M88">
-        <v>669.2206788</v>
+        <v>677.0023146</v>
       </c>
       <c r="N88">
-        <v>-577.1206788</v>
+        <v>-584.9023146</v>
       </c>
       <c r="O88">
-        <v>-103.881722184</v>
+        <v>-105.282416628</v>
       </c>
       <c r="P88">
-        <v>-473.238956616</v>
+        <v>-479.619897972</v>
       </c>
       <c r="Q88">
-        <v>-171.638956616</v>
+        <v>-178.019897972</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2666755583975445</v>
+        <v>0.2836659859665864</v>
       </c>
       <c r="T88">
-        <v>3.724279229182669</v>
+        <v>4.010762246812105</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02477209764307719</v>
+        <v>0.02448736088855906</v>
       </c>
       <c r="W88">
-        <v>0.2299587393757624</v>
+        <v>0.2300258803024778</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1376227646837622</v>
+        <v>0.1360408938253281</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2369990940388119</v>
+        <v>0.2388990940388119</v>
       </c>
       <c r="C89">
-        <v>-1908.983082559519</v>
+        <v>-1948.536187372184</v>
       </c>
       <c r="D89">
-        <v>728.3039174404809</v>
+        <v>721.7518126278161</v>
       </c>
       <c r="E89">
-        <v>2783.487</v>
+        <v>2816.488</v>
       </c>
       <c r="F89">
-        <v>2871.087</v>
+        <v>2904.088</v>
       </c>
       <c r="G89">
         <v>233.8</v>
@@ -8585,37 +8585,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M89">
-        <v>677.0023146</v>
+        <v>684.7839504</v>
       </c>
       <c r="N89">
-        <v>-584.9023146</v>
+        <v>-592.6839504</v>
       </c>
       <c r="O89">
-        <v>-105.282416628</v>
+        <v>-106.683111072</v>
       </c>
       <c r="P89">
-        <v>-479.619897972</v>
+        <v>-486.000839328</v>
       </c>
       <c r="Q89">
-        <v>-178.019897972</v>
+        <v>-184.400839328</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2836659859665864</v>
+        <v>0.3034881514638019</v>
       </c>
       <c r="T89">
-        <v>4.010762246812105</v>
+        <v>4.344992434046447</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02448736088855906</v>
+        <v>0.02420909542391634</v>
       </c>
       <c r="W89">
-        <v>0.2300258803024778</v>
+        <v>0.2300914952990405</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1360408938253281</v>
+        <v>0.1344949745773131</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2388990940388119</v>
+        <v>0.2407990940388119</v>
       </c>
       <c r="C90">
-        <v>-1948.536187372184</v>
+        <v>-1987.972452760047</v>
       </c>
       <c r="D90">
-        <v>721.7518126278161</v>
+        <v>715.3165472399529</v>
       </c>
       <c r="E90">
-        <v>2816.488</v>
+        <v>2849.489</v>
       </c>
       <c r="F90">
-        <v>2904.088</v>
+        <v>2937.089</v>
       </c>
       <c r="G90">
         <v>233.8</v>
@@ -8667,37 +8667,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M90">
-        <v>684.7839504</v>
+        <v>692.5655862</v>
       </c>
       <c r="N90">
-        <v>-592.6839504</v>
+        <v>-600.4655862</v>
       </c>
       <c r="O90">
-        <v>-106.683111072</v>
+        <v>-108.083805516</v>
       </c>
       <c r="P90">
-        <v>-486.000839328</v>
+        <v>-492.381780684</v>
       </c>
       <c r="Q90">
-        <v>-184.400839328</v>
+        <v>-190.781780684</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3034881514638019</v>
+        <v>0.3269143470514203</v>
       </c>
       <c r="T90">
-        <v>4.344992434046447</v>
+        <v>4.739991746232487</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02420909542391634</v>
+        <v>0.02393708311578245</v>
       </c>
       <c r="W90">
-        <v>0.2300914952990405</v>
+        <v>0.2301556358012985</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1344949745773131</v>
+        <v>0.1329837950876803</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2407990940388119</v>
+        <v>0.2426990940388119</v>
       </c>
       <c r="C91">
-        <v>-1987.972452760047</v>
+        <v>-2027.29497638604</v>
       </c>
       <c r="D91">
-        <v>715.3165472399529</v>
+        <v>708.9950236139597</v>
       </c>
       <c r="E91">
-        <v>2849.489</v>
+        <v>2882.49</v>
       </c>
       <c r="F91">
-        <v>2937.089</v>
+        <v>2970.09</v>
       </c>
       <c r="G91">
         <v>233.8</v>
@@ -8749,37 +8749,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M91">
-        <v>692.5655862</v>
+        <v>700.3472220000001</v>
       </c>
       <c r="N91">
-        <v>-600.4655862</v>
+        <v>-608.2472220000002</v>
       </c>
       <c r="O91">
-        <v>-108.083805516</v>
+        <v>-109.48449996</v>
       </c>
       <c r="P91">
-        <v>-492.381780684</v>
+        <v>-498.7627220400001</v>
       </c>
       <c r="Q91">
-        <v>-190.781780684</v>
+        <v>-197.1627220400001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3269143470514203</v>
+        <v>0.3550257817565624</v>
       </c>
       <c r="T91">
-        <v>4.739991746232487</v>
+        <v>5.213990920855737</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02393708311578245</v>
+        <v>0.02367111552560708</v>
       </c>
       <c r="W91">
-        <v>0.2301556358012985</v>
+        <v>0.2302183509590619</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1329837950876803</v>
+        <v>0.1315061973644838</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2426990940388119</v>
+        <v>0.2445990940388119</v>
       </c>
       <c r="C92">
-        <v>-2027.29497638604</v>
+        <v>-2066.506747371431</v>
       </c>
       <c r="D92">
-        <v>708.9950236139597</v>
+        <v>702.7842526285692</v>
       </c>
       <c r="E92">
-        <v>2882.49</v>
+        <v>2915.491</v>
       </c>
       <c r="F92">
-        <v>2970.09</v>
+        <v>3003.091</v>
       </c>
       <c r="G92">
         <v>233.8</v>
@@ -8831,37 +8831,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M92">
-        <v>700.3472220000001</v>
+        <v>708.1288578</v>
       </c>
       <c r="N92">
-        <v>-608.2472220000002</v>
+        <v>-616.0288578</v>
       </c>
       <c r="O92">
-        <v>-109.48449996</v>
+        <v>-110.885194404</v>
       </c>
       <c r="P92">
-        <v>-498.7627220400001</v>
+        <v>-505.143663396</v>
       </c>
       <c r="Q92">
-        <v>-197.1627220400001</v>
+        <v>-203.5436633959999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3550257817565624</v>
+        <v>0.389384201951736</v>
       </c>
       <c r="T92">
-        <v>5.213990920855737</v>
+        <v>5.793323245395264</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02367111552560708</v>
+        <v>0.02341099337697404</v>
       </c>
       <c r="W92">
-        <v>0.2302183509590619</v>
+        <v>0.2302796877617095</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1315061973644838</v>
+        <v>0.1300610743165226</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2445990940388119</v>
+        <v>0.2464990940388119</v>
       </c>
       <c r="C93">
-        <v>-2066.506747371431</v>
+        <v>-2105.610651008642</v>
       </c>
       <c r="D93">
-        <v>702.7842526285692</v>
+        <v>696.6813489913584</v>
       </c>
       <c r="E93">
-        <v>2915.491</v>
+        <v>2948.492</v>
       </c>
       <c r="F93">
-        <v>3003.091</v>
+        <v>3036.092</v>
       </c>
       <c r="G93">
         <v>233.8</v>
@@ -8913,37 +8913,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M93">
-        <v>708.1288578</v>
+        <v>715.9104936000001</v>
       </c>
       <c r="N93">
-        <v>-616.0288578</v>
+        <v>-623.8104936000002</v>
       </c>
       <c r="O93">
-        <v>-110.885194404</v>
+        <v>-112.285888848</v>
       </c>
       <c r="P93">
-        <v>-505.143663396</v>
+        <v>-511.5246047520002</v>
       </c>
       <c r="Q93">
-        <v>-203.5436633959999</v>
+        <v>-209.9246047520002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.389384201951736</v>
+        <v>0.4323322271957031</v>
       </c>
       <c r="T93">
-        <v>5.793323245395264</v>
+        <v>6.517488651069674</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02341099337697404</v>
+        <v>0.0231565260576591</v>
       </c>
       <c r="W93">
-        <v>0.2302796877617095</v>
+        <v>0.230339691155604</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1300610743165226</v>
+        <v>0.128647366986995</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2464990940388119</v>
+        <v>0.2483990940388119</v>
       </c>
       <c r="C94">
-        <v>-2105.610651008642</v>
+        <v>-2144.609473230636</v>
       </c>
       <c r="D94">
-        <v>696.6813489913584</v>
+        <v>690.6835267693648</v>
       </c>
       <c r="E94">
-        <v>2948.492</v>
+        <v>2981.493</v>
       </c>
       <c r="F94">
-        <v>3036.092</v>
+        <v>3069.093</v>
       </c>
       <c r="G94">
         <v>233.8</v>
@@ -8995,37 +8995,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M94">
-        <v>715.9104936000001</v>
+        <v>723.6921294000001</v>
       </c>
       <c r="N94">
-        <v>-623.8104936000002</v>
+        <v>-631.5921294000002</v>
       </c>
       <c r="O94">
-        <v>-112.285888848</v>
+        <v>-113.686583292</v>
       </c>
       <c r="P94">
-        <v>-511.5246047520002</v>
+        <v>-517.9055461080002</v>
       </c>
       <c r="Q94">
-        <v>-209.9246047520002</v>
+        <v>-216.3055461080002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4323322271957031</v>
+        <v>0.4875511167950893</v>
       </c>
       <c r="T94">
-        <v>6.517488651069674</v>
+        <v>7.448558458365343</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0231565260576591</v>
+        <v>0.0229075311538133</v>
       </c>
       <c r="W94">
-        <v>0.230339691155604</v>
+        <v>0.2303984041539308</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.128647366986995</v>
+        <v>0.1272640619656294</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2483990940388119</v>
+        <v>0.2502990940388119</v>
       </c>
       <c r="C95">
-        <v>-2144.609473230636</v>
+        <v>-2183.505904851397</v>
       </c>
       <c r="D95">
-        <v>690.6835267693648</v>
+        <v>684.7880951486035</v>
       </c>
       <c r="E95">
-        <v>2981.493</v>
+        <v>3014.494</v>
       </c>
       <c r="F95">
-        <v>3069.093</v>
+        <v>3102.094</v>
       </c>
       <c r="G95">
         <v>233.8</v>
@@ -9077,37 +9077,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M95">
-        <v>723.6921294000001</v>
+        <v>731.4737652</v>
       </c>
       <c r="N95">
-        <v>-631.5921294000002</v>
+        <v>-639.3737652</v>
       </c>
       <c r="O95">
-        <v>-113.686583292</v>
+        <v>-115.087277736</v>
       </c>
       <c r="P95">
-        <v>-517.9055461080002</v>
+        <v>-524.2864874639999</v>
       </c>
       <c r="Q95">
-        <v>-216.3055461080002</v>
+        <v>-222.6864874639999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4875511167950893</v>
+        <v>0.5611763029276042</v>
       </c>
       <c r="T95">
-        <v>7.448558458365343</v>
+        <v>8.689984868092901</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.0229075311538133</v>
+        <v>0.02266383401387913</v>
       </c>
       <c r="W95">
-        <v>0.2303984041539308</v>
+        <v>0.2304558679395273</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1272640619656294</v>
+        <v>0.1259101889659953</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2502990940388119</v>
+        <v>0.2521990940388119</v>
       </c>
       <c r="C96">
-        <v>-2183.505904851397</v>
+        <v>-2222.302545591092</v>
       </c>
       <c r="D96">
-        <v>684.7880951486035</v>
+        <v>678.9924544089082</v>
       </c>
       <c r="E96">
-        <v>3014.494</v>
+        <v>3047.495</v>
       </c>
       <c r="F96">
-        <v>3102.094</v>
+        <v>3135.095</v>
       </c>
       <c r="G96">
         <v>233.8</v>
@@ -9159,37 +9159,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M96">
-        <v>731.4737652</v>
+        <v>739.2554010000001</v>
       </c>
       <c r="N96">
-        <v>-639.3737652</v>
+        <v>-647.1554010000002</v>
       </c>
       <c r="O96">
-        <v>-115.087277736</v>
+        <v>-116.48797218</v>
       </c>
       <c r="P96">
-        <v>-524.2864874639999</v>
+        <v>-530.6674288200002</v>
       </c>
       <c r="Q96">
-        <v>-222.6864874639999</v>
+        <v>-229.0674288200001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5611763029276042</v>
+        <v>0.6642515635131255</v>
       </c>
       <c r="T96">
-        <v>8.689984868092901</v>
+        <v>10.42798184171149</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02266383401387913</v>
+        <v>0.02242526734004881</v>
       </c>
       <c r="W96">
-        <v>0.2304558679395273</v>
+        <v>0.2305121219612165</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1259101889659953</v>
+        <v>0.1245848185558267</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2521990940388119</v>
+        <v>0.2540990940388119</v>
       </c>
       <c r="C97">
-        <v>-2222.302545591092</v>
+        <v>-2261.001907898533</v>
       </c>
       <c r="D97">
-        <v>678.9924544089082</v>
+        <v>673.2940921014668</v>
       </c>
       <c r="E97">
-        <v>3047.495</v>
+        <v>3080.496</v>
       </c>
       <c r="F97">
-        <v>3135.095</v>
+        <v>3168.096</v>
       </c>
       <c r="G97">
         <v>233.8</v>
@@ -9241,37 +9241,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M97">
-        <v>739.2554010000001</v>
+        <v>747.0370368</v>
       </c>
       <c r="N97">
-        <v>-647.1554010000002</v>
+        <v>-654.9370368</v>
       </c>
       <c r="O97">
-        <v>-116.48797218</v>
+        <v>-117.888666624</v>
       </c>
       <c r="P97">
-        <v>-530.6674288200002</v>
+        <v>-537.0483701759999</v>
       </c>
       <c r="Q97">
-        <v>-229.0674288200001</v>
+        <v>-235.4483701759999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6642515635131255</v>
+        <v>0.8188644543914071</v>
       </c>
       <c r="T97">
-        <v>10.42798184171149</v>
+        <v>13.03497730213937</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02242526734004881</v>
+        <v>0.02219167080525665</v>
       </c>
       <c r="W97">
-        <v>0.2305121219612165</v>
+        <v>0.2305672040241205</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1245848185558267</v>
+        <v>0.1232870600292036</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2540990940388119</v>
+        <v>0.2559990940388119</v>
       </c>
       <c r="C98">
-        <v>-2261.001907898533</v>
+        <v>-2299.606420582775</v>
       </c>
       <c r="D98">
-        <v>673.2940921014672</v>
+        <v>667.6905794172251</v>
       </c>
       <c r="E98">
-        <v>3080.496</v>
+        <v>3113.497</v>
       </c>
       <c r="F98">
-        <v>3168.096</v>
+        <v>3201.097</v>
       </c>
       <c r="G98">
         <v>233.8</v>
@@ -9323,37 +9323,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M98">
-        <v>747.0370368</v>
+        <v>754.8186726</v>
       </c>
       <c r="N98">
-        <v>-654.9370368</v>
+        <v>-662.7186726</v>
       </c>
       <c r="O98">
-        <v>-117.888666624</v>
+        <v>-119.289361068</v>
       </c>
       <c r="P98">
-        <v>-537.0483701759999</v>
+        <v>-543.429311532</v>
       </c>
       <c r="Q98">
-        <v>-235.4483701759999</v>
+        <v>-241.829311532</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.818864454391405</v>
+        <v>1.076552605855207</v>
       </c>
       <c r="T98">
-        <v>13.03497730213933</v>
+        <v>17.37996973618577</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02219167080525665</v>
+        <v>0.02196289069386224</v>
       </c>
       <c r="W98">
-        <v>0.2305672040241205</v>
+        <v>0.2306211503743873</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1232870600292036</v>
+        <v>0.1220160594103459</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2559990940388119</v>
+        <v>0.2578990940388119</v>
       </c>
       <c r="C99">
-        <v>-2299.606420582775</v>
+        <v>-2338.118432264859</v>
       </c>
       <c r="D99">
-        <v>667.6905794172251</v>
+        <v>662.1795677351408</v>
       </c>
       <c r="E99">
-        <v>3113.497</v>
+        <v>3146.498</v>
       </c>
       <c r="F99">
-        <v>3201.097</v>
+        <v>3234.098</v>
       </c>
       <c r="G99">
         <v>233.8</v>
@@ -9405,37 +9405,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M99">
-        <v>754.8186726</v>
+        <v>762.6003084</v>
       </c>
       <c r="N99">
-        <v>-662.7186726</v>
+        <v>-670.5003084</v>
       </c>
       <c r="O99">
-        <v>-119.289361068</v>
+        <v>-120.690055512</v>
       </c>
       <c r="P99">
-        <v>-543.429311532</v>
+        <v>-549.810252888</v>
       </c>
       <c r="Q99">
-        <v>-241.829311532</v>
+        <v>-248.210252888</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.076552605855207</v>
+        <v>1.59192890878281</v>
       </c>
       <c r="T99">
-        <v>17.37996973618577</v>
+        <v>26.06995460427866</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02196289069386224</v>
+        <v>0.02173877956433304</v>
       </c>
       <c r="W99">
-        <v>0.2306211503743873</v>
+        <v>0.2306739957787303</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1220160594103459</v>
+        <v>0.1207709975796281</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2578990940388119</v>
+        <v>0.2597990940388119</v>
       </c>
       <c r="C100">
-        <v>-2338.118432264859</v>
+        <v>-2376.540214660021</v>
       </c>
       <c r="D100">
-        <v>662.1795677351408</v>
+        <v>656.758785339979</v>
       </c>
       <c r="E100">
-        <v>3146.498</v>
+        <v>3179.499</v>
       </c>
       <c r="F100">
-        <v>3234.098</v>
+        <v>3267.099</v>
       </c>
       <c r="G100">
         <v>233.8</v>
@@ -9487,37 +9487,37 @@
         <v>92.09999999999997</v>
       </c>
       <c r="M100">
-        <v>762.6003084</v>
+        <v>770.3819441999999</v>
       </c>
       <c r="N100">
-        <v>-670.5003084</v>
+        <v>-678.2819442</v>
       </c>
       <c r="O100">
-        <v>-120.690055512</v>
+        <v>-122.090749956</v>
       </c>
       <c r="P100">
-        <v>-549.810252888</v>
+        <v>-556.191194244</v>
       </c>
       <c r="Q100">
-        <v>-248.210252888</v>
+        <v>-254.591194244</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.59192890878281</v>
+        <v>3.13805781756562</v>
       </c>
       <c r="T100">
-        <v>26.06995460427866</v>
+        <v>52.13990920855732</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02173877956433304</v>
+        <v>0.02151919593237008</v>
       </c>
       <c r="W100">
-        <v>0.2306739957787303</v>
+        <v>0.2307257735991471</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1207709975796281</v>
+        <v>0.1195510885131671</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2597990940388119</v>
-      </c>
-      <c r="C101">
-        <v>-2376.540214660021</v>
-      </c>
-      <c r="D101">
-        <v>656.758785339979</v>
-      </c>
-      <c r="E101">
-        <v>3179.499</v>
-      </c>
-      <c r="F101">
-        <v>3267.099</v>
-      </c>
-      <c r="G101">
-        <v>233.8</v>
-      </c>
-      <c r="H101">
-        <v>3212.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>393.7</v>
-      </c>
-      <c r="K101">
-        <v>301.6</v>
-      </c>
-      <c r="L101">
-        <v>92.09999999999997</v>
-      </c>
-      <c r="M101">
-        <v>770.3819441999999</v>
-      </c>
-      <c r="N101">
-        <v>-678.2819442</v>
-      </c>
-      <c r="O101">
-        <v>-122.090749956</v>
-      </c>
-      <c r="P101">
-        <v>-556.191194244</v>
-      </c>
-      <c r="Q101">
-        <v>-254.591194244</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.13805781756562</v>
-      </c>
-      <c r="T101">
-        <v>52.13990920855732</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02151919593237008</v>
-      </c>
-      <c r="W101">
-        <v>0.2307257735991471</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1195510885131671</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
